--- a/course-design-2/data/interim/skill_annotation_sample.xlsx
+++ b/course-design-2/data/interim/skill_annotation_sample.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_标注表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_分层构成" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_抽样说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_标注表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_分层构成" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_抽样说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,17 +458,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>全文兜底原文（节选）</t>
+          <t>全文回退原文（节选）</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>规则抽取_要求段口径</t>
+          <t>规则抽取_要求段统计范围</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>规则抽取_扩展口径</t>
+          <t>规则抽取_扩展统计范围</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">

--- a/course-design-2/data/interim/skill_annotation_sample.xlsx
+++ b/course-design-2/data/interim/skill_annotation_sample.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_标注表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_分层构成" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_抽样说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_标注表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_分层构成" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_抽样说明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>全文回退原文（节选）</t>
+          <t>全文兜底原文（节选）</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -518,15 +518,11 @@
           <t>About our team The Clienteling team is a team under LVMH Digital. We aim to provide better client development tools and intelligence to our front-line client advisors to increase retail efficiency from digital perspective. Job Duties As an intern of Clienteling team, you will be involved in all the projects with Maisons and provide support along the project period. Key responsibilities： - Track detailed project status for each Maison - Document all meeting materials and meeting minutes - Test AI generated content, give concrete feedback and collect business users’ feedback - Assist in organizi</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Excel、PPT、人工智能</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,9 +565,6 @@
           <t>AIGC、PyTorch、Python、大模型、深度学习</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -604,11 +597,6 @@
           <t>1. Assist the production supervisor to do the production arrangement 2. Support the Upstream administrative support work, data handling Engineering Background（Mechanical, electrical or material major)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -651,9 +639,6 @@
           <t>CSS、HTML、JavaScript、Node.js、React、Vue、Webpack、前端</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -696,9 +681,6 @@
           <t>Agent、Prompt Engineering、Python、人工智能、大模型</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -731,11 +713,6 @@
           <t>工作模式：全程线上，无需打卡，只要按时交付成果，早八晚五还是深夜工作随你。 【职位详情】 时间地点不限！不坐班，线上工作！！！非线下，时间自由，灵活实习、可提供实习证明 【工作内容】 1、不用自己写！有网感即可！根据公司提供的图文，进行内容的小红书&amp;抖音等相关的内容种草、笔记代发。 2、能及时沟通，关注自己的平台账号实时动向。确保账号权重优质，会有工作人员带教！ 【岗位要求】 1、有小红书&amp;抖音实名账号优先 2、小红书、抖音等新媒体平台重度用户，了解平台的流量机制。</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -778,9 +755,6 @@
           <t>Excel、SQL、数据可视化、物联网</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -813,15 +787,11 @@
           <t>一、岗位描述 1、负责品牌自媒体矩阵（公众号、小红书、微博、抖音、视频号等）的运营及内容输出； 2、能独立创意策划制作图文/视频素材，具备拍摄能力和剪辑能力； 3、及时捕捉热点信息，并进行资料搜集与编辑整理； 4、定期策划并执行线上及线下内容，提高粉丝关注度、活跃度、互动率和粘性，同时提高账号影响力。 二、岗位要求 1、27、28届本科以上学历，新闻类、中文类、营销类专业优先，有新媒体账号运营经验者优先； 2、具有敏锐的新媒体嗅觉，能够掌握当下热点； 3、熟悉基础办公软件，具备一定的文字写作能力和图片、视频处理能力； 4、具有良好的沟通能力、组织协调能力、团队意识以及执行能力。 实习要求 5天/周*3个月</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -854,15 +824,11 @@
           <t>【岗位职责】 1. 核心系统研发：基于 Golang 构建高可用的后端服务，参与分布式系统架构的设计与落地，挑战海量数据处理与高并发场景下的技术难题。 2. 全栈式交付：在后端逻辑实现的基础上，利用 AI 编程工具（如 Cursor、Copilot 等）高效完成简单的前端页面开发，实现功能的端到端交付。 3. 极致性能优化：深入理解业务痛点，对核心接口进行性能调优，解决分布式环境下的数据一致性、服务熔断降级及链路追踪等问题。 4. AI 工作流探索：作为团队内的“AI先锋”，积极探索并应用各类 AI 辅助工具（如 ChatGPT、Claude 等）来提升编码效率、生成测试数据、优化代码逻辑。 【任职要求】 1. 基础扎实：本科及以上在读（计算机相关专业），掌握常见的数据结构与算法，具有良好的编程习惯。 2. Golang 熟练：熟悉 Golang 语言特性（如 Goroutine, Channel 等），了解 Gin/Echo 等常用 Web 框架，有实际项目经验者优先。 3. AI 驾驶能力：具备“AI-Native”的工作思维(强需求)。不仅能熟练使用 AI 工具，更懂得如何通过 Prompt（提示词）让 AI 生成可用的前端代码（HTML/CSS/Vue/React 等），即使你本身不是前端工程师，也能借助 AI 独立完成简单的全栈模块。 4. 学习能力：对新技术充满好奇心，</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>CSS、Docker、Git、Go、HTML、Kafka、Linux、MySQL、Prompt Engineering、React、Redis、Vue、人工智能、全栈、前端、后端、大模型</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -895,11 +861,6 @@
           <t>职位亮点：电商对你来说不仅仅是买买买和卖卖卖，而是基于新一代营销和大数据趋势的智慧平台，如果你也这样理解电商，欢迎加入我们。新趋势：能接触众多有设计感的北欧品牌；大视野：完整体验品牌运营流程；新技术：提前接触新一代的融合电商，表现优异者可转正实习 职位描述 1. 产品分析：研究品牌和产品，参与产品定位及卖点分析； 2. 数据挖掘：基于天猫大数据平台及公司自有的全平台大数据工具分析行业、类目、竞品现状，参与制定高效地运营策略； 3. 活动运营：协同品牌市场部，协助策划和制定平台和店铺的营销策划活动； 4. 日常运营：根据资深电商总监的安排体验和支持跨境电商全流程的日常运营； 任职要求： 1. 专业及学历：计算机、电子商务、市场营销等相关专业，大三、大四或研二、研三优先 2. 职业规划：对新一代的电子商务、市场营销有强烈好奇并愿意投身其中的同学 3. 综合素质：对未知的世界一直充满好奇，相信人生是充满挑战的奇妙旅行</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -932,15 +893,11 @@
           <t>聘工（上海）人力资源有限公司，立足上海市，苏州等地。我们是一家聚焦中高端制造业以及幼师，酒店等集制造，教育，酒店服务等实习加就业岗位的校企合作机构。公司汇聚了来自江浙地区多家汽车，芯片，新能源，教培，中高端酒店等知名企业的长期人才梯队培 养需求，达成企业方和高校共同搭建人才储备培养平台。 我们深知实习不仅是实践，更是未来职业的铺垫。公司提供极具竞争力的实习待遇，和完善培养机制及深入学习HR专业技能 招聘岗位： 人事招聘专员（高校端）2人 岗位内容：招聘演讲，招聘会活动联系协调，面试筛选，信息汇总，入离职办理，员工关系等模块 薪资福利： 实习期基本薪3500+500补贴+招聘完成率绩效提成 实习期4000~7000。转正后综合5000~9000.上海五险一金 提供宿舍 岗位特性：仪表端正 谈吐清晰，性格主动开朗，能接受全国出差。有明确的追求目标，拒绝躺平和迷茫人生。熟悉office 基本表格 汇总等数据登记，汇总，归类 筛选等操作</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -973,15 +930,11 @@
           <t>ByteIntern：面向2027届毕业生（2026年9月-2027年8月期间毕业），为符合岗位要求的同学提供转正机会。 团队介绍：抖音电商致力于成为用户发现丰富好物的首选平台。众多抖音创作者通过短视频、直播、商城等丰富的形式，给用户提供更个性化、更生动、更高效的消费体验。同时，抖音电商积极引入优质合作伙伴，为商家变现提供多元的选择。 1、参与抖音电商物流服务及解决方案设计，基于供给与商业诉求，设计适配业务场景的物流解决方案； 2、深入洞察和理解用户诉求，参与发掘不同业务特点与模式下的物流服务机会点，为平台带来增量价值； 3、拆解复杂问题，协调各方资源，与内外部团队紧密合作，推动跨团队需求及项目管理； 4、结合业务重心和目标，定期输出产品迭代规划，驱动业务目标达成。 职位要求 1、2027届本科及以上学历在读，统计学、物流、数学、计算机等理工科专业背景优先； 2、逻辑思维极其严密，具备优秀的系统性思维和业务抽象能力，善于发现和提炼共性； 3、熟练使用SQL，能深入理解业务流程，有To B产品、平台产品或中台产品实习经验者优先； 4、能保证到9月底之前实习满3个月，能尽快到岗优先。</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>SQL、项目管理</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1014,15 +967,11 @@
           <t>你可以体验到： - 参与地图泛娱乐IP合作项目的内容上线和推广传播，如时下热门影视综及游戏IP等合作 - 通过竞品分析和用户反馈，不断打磨内容及产品质量，探索并策划相关产品玩法 - 负责泛娱乐IP新媒体传播 - 完成相关运营活动配置及上线工作，协同完成组内其他项目执行落地 我们希望你是： - 对于娱乐热点敏感或者有游戏经历，关注流行趋势，对明星娱乐、二次元方向了解 - 责任感强，做事细致，善于思考，沟通及抗压能力强 - 熟练使用办公软件、较强的文字功底 - 每周到岗5天，实习期至少5个月，实习稳定优先，有相关实习经验优先 - 大学本科或研究生在读，2027年及以后毕业</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>办公软件、市场调研</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1065,9 +1014,6 @@
           <t>Excel、PPT</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1110,9 +1056,6 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1145,15 +1088,11 @@
           <t>1、在读本科/硕士 2、对用户洞察感兴趣，喜欢和用户打交道，能深入用户 3、有较好运营数据分析处理能力、 有较好的语言沟通和文字表达能力 4、有互联网运营相关经验优先 5、逻辑性强，执行力佳，有责任心 岗位职责 1、深度参与快应用中心的日常运营，包括拉新、激活、留存及转化路径，优化产品功能体验，提升产品活力 2、关注行业动态、同类产品动向，推动运营策略迭代，促进业务发展; 3、推动相关产品和服务团队按计划落实运营规划，并最终反馈到产品及服务质量提升。</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1186,11 +1125,6 @@
           <t>按单结算！线上发抖音视频！护肤品/彩妆类合作的来，坚持发可开实习证明！ 【工作内容】 1、不用自己写！有网感即可！根据公司提供的图文，进行内容的小红书/抖音等相关的内容种草、笔记代发。 2、能及时沟通，关注自己的平台账号实时动向。确保账号权重优质，会有工作人员带教！ 【职位详情】 时间地点不限！不坐班，线上工作！！！非线下，按单结算 【岗位要求】 1、有小红书/抖音实名账号优先 2、小红书、抖音等新媒体平台重度用户，了解平台的流量机制！</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1233,9 +1167,6 @@
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1278,9 +1209,6 @@
           <t>Excel、Word、办公软件</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1313,11 +1241,6 @@
           <t>Be part of a team that designs, develops and integrates highly complex software functions within Honeywell AERO. You will use your experience and judgment to plan and accomplish goals. You will also generate innovative solutions in work situations; trying different and novel ways to deal with problems and opportunities. Key Responsibilities The selected candidate will be mostly working in IFS (Integrated Flight-Deck System), FS (Flight System) and CNS (Communication, Navigation and Surveillance) product lines within Software Verification &amp; Validation (SW V&amp;V) in China and performing system/sof</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1360,9 +1283,6 @@
           <t>Excel、办公软件</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1395,11 +1315,6 @@
           <t>【工作内容】 参与雇主品牌传播策略的脑暴，输出具有传播力的创意内容（如招聘海报、宣传视频脚本、员工故事推文、互动游戏等）。 结合校招/社招节点，策划创意招聘宣传方案，通过有吸引力的内容触达目标候选人。 协助运营官方招聘新媒体（公众号、小红书、B站等），策划创意专栏或系列内容。 【任职要求】 广告、市场营销、新闻传播、心理学、人力资源等相关专业优先。 有新奇点子，能将普通的活动/内容玩出新花样，有策划过校园活动或小型项目的经验优先。 面试请准备个人原创作品（拒绝纯模板套用作品）。</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1432,15 +1347,11 @@
           <t>1、从事生成式AI方向的算法探索和落地开发； 2、负责视觉生成基础模型的框架设计与预训练，以及面向实际应用的调优；研发方向包括但不限于图像/视频/3D图形的生成。</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>AIGC</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1473,15 +1384,11 @@
           <t>ByteIntern：面向2027届毕业生（2026年9月-2027年8月期间毕业），为符合岗位要求的同学提供转正机会。 团队介绍：抖音电商致力于成为用户发现丰富好物的首选平台。众多抖音创作者通过短视频、直播、商城等丰富的形式，给用户提供更个性化、更生动、更高效的消费体验。同时，抖音电商积极引入优质合作伙伴，为商家变现提供多元的选择。 1、跟进并优化逆向退货操作标准流程，明确快递服务商在退货各环节的职责、操作规范与时间要求； 2、熟悉全面的逆向退货运营体验指标体系，涵盖退货揽收及时率、客户投诉率、退货处理时效等关键指标； 3、每日、每周、每月收集、整理并分析指标数据，及时发现潜在风险与异常波动，形成可视化数据报表和分析报告；通过分析发现某地区退货揽收超时严重，可针对性优化当地物流合作策略。 职位要求 1、2027届本科及以上学历在读，数学/商业分析/物流专业/统计学等相关专业优先； 2、对抖音电商有一定了解，有电商实习经验优先； 3、具备较强逻辑思考能力和数据分析能力，熟练使用Excel和SQL及可视化分析工具； 4、良好的沟通表达能力，学习能力强、自驱导向、责任心强，积极主动，敢于接受挑战。</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Excel、SQL、数据分析、数据可视化、数据运营</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1514,11 +1421,6 @@
           <t>工作内容 1、负责电源硬件的设计、开发与优化，确保产品质量和性能。 2、参与电源硬件的测试工作，与团队协作确保功能的稳定性和可靠性。 3、根据项目需求，进行电源硬件的成本控制和资源分配。 任职要求 1、具备扎实的电源硬件知识，能够独立解决硬件开发中的技术难题。 2、具有良好的团队合作精神，能够与团队成员有效沟通。 3、对工作有高度的责任心，能够在项目压力下保持良好的工作状态。</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1551,15 +1453,11 @@
           <t>岗位职责 1. 深度参与订单匹配流程，运用数据分析识别匹配效率瓶颈，挖掘优化空间。 2. 协同算法团队，优化匹配策略，设计高效订单分配与推荐算法，提升匹配精准度。 3. 协同运营团队，依据市场动态与用户行为，灵活调整匹配规则，提升用户体验。 4. 通过A/B测试等方法验证匹配策略效果，以数据驱动产品持续优化。 职位要求 1. 对数据敏感，能迅速捕捉供需动态变化，洞察匹配潜在规律。 2. 具备产品思维，擅长将复杂业务场景转化为清晰产品方案。 3. 掌握Axure、SQL等工具，为策略与产品优化提供支持。 4. 具备跨部门沟通协作能力，能与技术、运营等团队高效协作，推动项目落地。</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>SQL、产品设计、原型设计、推荐系统、数据分析</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1592,15 +1490,11 @@
           <t>岗位职责 1、 协助处理签证申请材料审核、整理及归档； 2、跟进签证进度，与使领馆或第三方服务机构沟通； 3、解答员工签证咨询，提供流程指导； 4、协助更新签证政策数据库，整理各国签证要求； 5、支持团队完成其他行政或协调工作。 任职资格 1、在校本科生及以上学历，专业不限（国际商务、外语、旅游管理、法律、行政管理等相关专业优先）。 2、语言能力：英语四级及以上（或同等水平），能熟练阅读英文文件； 3、实习时间不少于三个月，每周出勤5天； 4、熟练使用Office办公软件（Excel、Word、PPT），具备基础数据处理能力； 5、有基础的法律知识或签证政策了解者优先。善于沟通、坚韧抗压、有耐心、自我驱动性较强； 6、良好的文字表达和沟通能力，能清晰对接员工或使领馆</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Excel、PPT、Word、办公软件</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1633,15 +1527,11 @@
           <t>【职位描述】 1、负责B站会员购中潮玩ACG行业商家的日常建联，协助商家入驻平台与商品上架等工作； 2、负责商家的日常维护，跟踪店铺的商品情况与销售数据，多维度优化商家运作； 3、负责大促活动期间的商家招商、货品盘点、数据追踪、资源位素材制作等工作，协助部门的活动落地、运营与复盘； 【任职要求】 1、本科及以上学历，有互联网行业相关经验优先； 2、数据敏感，熟练使用office办公软件； 3、审美在线，会使用PS等设计软件； 4、负责靠谱、善于沟通、团队意识强。</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1674,11 +1564,6 @@
           <t>关于我们 博世集团（Bosch Group）成立于1886年，全称是罗伯特·博世有限公司（BOSCH），是工业技术、消费品和能源及建筑技术的产业。博世公司以其创新尖端的产品及系统解决方案闻名于世。 博世集团是全球第一大汽车技术供应商，员工人数超过 42万，遍布 50 多个国家。2022年销售额达到884亿欧元，其中在中国销售额达到1323亿人民币。 2018年7月19日，《世界500强排行榜发布，博世集团位列75位。2022年12月，位列《2022胡润世界500强》第58位。 职责描述: ﻿1.改善目前的iEHS系统在使用过程反馈的问题，进一步优化系统使用 2.将现有HSE 记录电子化，提高数字化率 3.协助跟进落实公司进行的可持续发展的措施 4.协助推进公司的绿色项目 5.HSE公共盘架构及文件的整理 6.其他支持性工作 岗位要求: 1.具备良好的英语书面表达能力。 2.熟悉EHS管理及ISO 14001/45001体系相关知识。 3.良好的沟通技能及主动性 福利: 500强外企，跨文化交流，大平台新视野。 公司有食堂，工作氛围轻松愉快，可优先接触内部转正机会！ 与行业专家一对一指导，快速提升专业技能和职场竞争力。 在世界百强外企中积累宝贵的实习经验，为你的简历增色。 投递岗位即默认同意博世集团网上招聘相关隐私协议 协议地址：请通过访问博世中国官方主页，博世在中国＆gt;加入博世</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1711,11 +1596,6 @@
           <t>职责：协助部门做好各类活动策划和组织落实；协助视频、音频剪辑等；协助处理好其他日常活动 要求：本科及以上，数字媒体等相关专业优先，熟练使用视频或音频剪辑软件，学习能力优秀，逻辑清晰，一周能实习3天及以上</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1758,9 +1638,6 @@
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1803,9 +1680,6 @@
           <t>Excel、PPT、办公软件、数据分析、项目管理</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1838,15 +1712,11 @@
           <t>【职位详情】 1.产品建模及渲染(C4D及Redshift渲染器) 2.产品场景合成(Photoshop) 3.点/面跟踪，抠像(AfterEffects) 【任职要求】 1.数字媒体、产品设计、视觉传达等相关专业，有建模能力优先 2.会基本的PS、C4d及AfterEffects 3.学习能力和执行能力强 4.简历附上相关设计作品</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1889,9 +1759,6 @@
           <t>Agent、Prompt Engineering、人工智能、大模型</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1924,15 +1791,11 @@
           <t>We are seeking an .Net Intern to join our team, providing hands-on experience in designing and developing cloud-based solutions using Azure, SQL Server, ASP.NET, and C#. This internship offers an excellent opportunity to gain practical skills in backend development and cloud infrastructure while contributing to our IT systems. Responsibilities: • Assist in designing and developing scalable, secure, and efficient cloud-based solutions. • Participate in team meetings and contribute to discussions on project requirements. • Support database optimization tasks under supervision. • Help develop RES</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>C#、CI/CD、DevOps、RESTful API、SQL Server</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1965,15 +1828,11 @@
           <t>Please send us your 作品集！ We at Orient Path helps foreign businesses to strategically do business with China！ About the Role: We‘re looking for a creative, hungry content intern to help grow a founder’s social media presence across **YouTube and Instagram** (short-form + long-form). What You’ll Do * Edit short-form videos (Reels / Shorts style) * Edit long-form YouTube content * Assist with filming * Brainstorm content ideas, hooks, and formats * Stay on top of trends and help optimize performance What We’re Looking For * Fluent in English, Overseas exp. is a major plus! * Experience with video</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2006,15 +1865,11 @@
           <t>职位描述 1、负责对接主播和公会，处理日常问题，优化主播和公会体验； 2、协助正职线上建联招募优质主播和公会，对收入、开播规模、主播质量等指标负责； 3、归纳主播和公会的成长路径和方法论，建立标杆效应，驱动公会和主播健康发展； 4、监控各项数据，输出报表和报告，确保指标正常运转。 任职要求 1、直播深度粉丝，研二或大三的同学优先，每周实习5天，至少实习5个月以上。 能立即到岗/稳定全勤者优先； 2、抗压能力强，可以接受加班，热情主动，有责任心，有良好的沟通能力； 3、熟练掌握EXCEL，使用数据透视等输出数据结果，工作细致，有数据敏感度。</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2057,9 +1912,6 @@
           <t>内容运营</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2092,15 +1944,11 @@
           <t>工作职责:职位介绍：1、负责B站大会员业务前端开发工作；2、工作范围涉及前端基础架构、跨端应用、全栈开发、数据可视化、中后台等多个方向；3、与产品经理、设计师、后端工程师一起，提升产品的用户体验，打造卓越的互联网产品；工作要求:职位要求：1. 对计算机专业相关基础知识掌握牢固，诸如常见数据结构与算法，专业基础常识等内容2. 对 Web 前端开发技能熟练掌握，包括诸如 HTML、样式表、JavaScript 编程等基础内容与额外积累的开发技能与经验3. 熟悉主流框架（ React、Vue3、Vue2 ）中的一种或多种并拥有实战开发经验4. 熟练使用git 各种命令。熟悉Typescript，能使用类型来提升项目可维护性5. 有过前端实习经验优先</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Git、HTML、JavaScript、React、TypeScript、Vue、全栈、前端、后端、数据可视化</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2133,15 +1981,11 @@
           <t>岗位职责 1、数据监控：协助监控业务数据波动，发现并分析业务问题，针对项目需求进行数据分析，提供可视化的数据报告； 2、需求收集：用户需求收集和整理，协助优化业务运营策略和产品设计； 3、策略运营：基于发现的问题，协助制定和发布对应的策略，整体提升业务指标。 任职资格 1、对于互联网策略和用户运营有基本认知和兴趣； 2、熟练使用Excel、SQL等相关数据提取工具，能够基于数据产出可视化的分析报告； 3、细心、责任心强、对结果负责，具有良好的自我驱动能力、抗压能力； 4、善于沟通，具有良好的团队合作精神； 5、能尽快到岗，一周需全职实习5天，连续实习3个月以上，实习期间需为在校生身份（尚未取得毕业证书）； 6、线上面试，入职后需到广州琶洲办公。 7、！！！需要能流利听说【粤语】以及【繁体字】阅读。</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Excel、SQL、产品设计、数据分析、数据可视化</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2174,15 +2018,11 @@
           <t>团队介绍：快手特效团队负责快手生产和直播等核心业务的特效技术能力研发，致力于通过多模态大模型与新技术结合，提升用户“美”和“有意思”的创作体验。 1、负责特效方向多模态大模型的研发、调优和应用，包括但不限于文本/图像/视频理解和生成； 2、将大模型能力在公司核心业务场景中应用落地，如智能化特效、AIGC创意生成等。</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>AIGC、人工智能、多模态、大模型</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2215,15 +2055,11 @@
           <t>职位描述1、负责B端数据分析，基于数据洞察，进行规范化指导； 2、负责B端经营管理与培训，并收集进度与反馈； 3、设计和策划线上线下活动，提高运营效率。任职要求1、本科及以上学历，沟通能力强、强目标导向，抗压能力强，执行力和推动力强； 2、具备数据分析能力，熟练使用Excel（如数据透视表、基础函数等），能够根据数据调整运营策略； 3、有大厂直播业务实习经历优先；实习半年以上优先。</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Excel、数据分析</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2266,9 +2102,6 @@
           <t>CSS、Git、HTML、Java、JavaScript、Spring、Spring Boot、Vue、前端、后端、项目管理</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2301,15 +2134,11 @@
           <t>1、协助校园招聘广告渠道的运行和供应商的对接； 2、整理校园生源就业信息，调研校园招聘人才情况； 3、协助校园招聘高校活动落地，运营社群/小助手账号； 4、协助进行人力资源相关的数据统计工作； 5、支持校招Team其他事宜，如雇主品牌支持和宣传等任职要求 1、25届及以后毕业的本科或研究生，不限专业； 2、英语水平优秀，达到雅思7分或六级550以上者优先； 3、熟练运用 Excel、Word、PPT等办公软件； 4、踏实工作、积极上进、认真细心、有责任感、乐观自省、学习能力强； 5、能够连续实习4个月及以上，每周出勤4天及以上者优先 6、有学校组织或校园社团管理经历，活动策划和组织经验，人力资源实习经历为加分项； 注：日常实习，无转正</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Excel、PPT、Word、办公软件</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2342,15 +2171,11 @@
           <t>工作职责 1，采购业务对账及结算 2，熟悉全采购流程并在系统操作 3，数据分析及报告撰写 任职要求， 1、财务专业优先 2、良好的沟通能力，学习能力，应变能力 3、熟悉SAP、ERP等系统操作</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2383,15 +2208,11 @@
           <t>非应届（27年及以后毕业），可以实习五个月以上，每周四天以上 岗位职责（具体工作内容） 1. 与算法团队深度配合，基于多模态大模型等多种能力，挖掘高价值场景； 2. 研发数据检索和挖掘平台，支持算法团队便捷高效地自主挖掘数据； 3. 构建数据存取、分析、管理和可视化等一系列工具，让分析流程的更高效，更自动，更用户友好。 任职资格（学历、目标院校、语言、技能、性格等要求） 1. 计算机、统计学、数学等相关专业教育背景，良好的机器学习、统计学、数学知识; 2. 熟悉使用至少一门主流编程语言，如Python/C++; 3. 具备很强的逻辑性和业务理解力，较强的沟通交流和团队合作能力，能够主动积极的探索方向。 有如下经验者优先： - 大规模驾驶数据库的分析处理等经验; - 大模型应用与优化相关经验； - 数据挖掘和机器学习算法相关经验； - 熟练使用数据处理、分析和可视化库，熟练使用SQL； - 熟悉大数据生态工具，如Hive, spark等。</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>C++、Hive、Python、SQL、Spark、多模态、大数据、大模型、数据可视化、数据挖掘、机器学习</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2424,11 +2245,6 @@
           <t>岗位职责: 1.负责B端市场新媒体平台内容运营，持续跟踪与餐饮行业及平台相关的内容趋势。 2.参与热点话题与典型内容的整理与复盘，总结内容传播与互动规律，形成可复用的运营经验。 3.负责新媒体内容策划与产出，包括公众号推文、短视频脚本、宣传物料等。 4.协助设计培训课程内容，整理业务知识、服务标准及运营流程等资料 5.支持线上线下培训活动的组织与实施，包括场地安排、材料准备和现场协调。 岗位要求: 1.文笔优秀，新闻、中文专业优先. 2.熟悉主流新媒体与短视频平台的内容生态与互动机制。 3.具备年轻化传播思维，有网感和活力，良好的文字表达能力。 4.执行力强、善于思考、自驱力强、乐于学习。 岗位亮点: 全方位了解美团多条核心业务线；提供给学生成长机会和学习的组织氛围；团队nice，好玩有趣。</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2471,9 +2287,6 @@
           <t>Excel、PPT、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2506,15 +2319,11 @@
           <t>实习分析师岗位包含大数据与投研两个方向： 【岗位职责】 ****** 投研方向 ****** - 定期跟踪和分析全球宏观经济走势、资产大类表现、行业热点变化，优化与维护量化指标分析Python脚本，识别市场趋势与潜在投资机会，输出有价值观点。 - 跟踪数据库、大数据分析和人工智能领域的最新技术趋势、关键产品及商业进展。 ****** 大数据产业研究方向 ****** - 跟踪数据库、大数据分析和人工智能领域的最新技术趋势、关键产品及商业进展，涵盖领域包括云数据库、大数据处理平台、流式数据分析技术、多模态大型模型等。 - 每周负责： 1. 梳理技术产品、商业领域、开源、初创和产业链的热点话题和重要讯息，输出有价值观点； 2. 围绕技术趋势、产品动态、公司经营或行业走向等专题，撰写洞察分析报告。 【岗位亮点】 - 大数据行业资深专家直接指导，学习500强企业的战略分析技巧，掌握行业领先技术知识和深度思考。 - 持续接触并研究全球最前沿技术和资讯，掌握量化分析与宏观研判结合的方法论。 - 亲身参与资产配置与管理，通过系统化实践锻炼，培养投资素养和财富管理能力。 【岗位待遇】 - 工资根据个人产出按月结算。 - 提供远程办公机会，工作时间灵活，无需到办公室坐班或打卡。 - 实习结束后，可提供实习证明或推荐信。 【岗位要求】 - 计算机、大数据、经济学及相关专业本科及以上在读，对大数据技术及</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Git、Matplotlib、Pandas、Python、人工智能、多模态、大数据、数据分析</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2547,15 +2356,11 @@
           <t>工作内容：协助进行英语短期盒子课程研发、审校工作，校对教材教辅中的听力、音频、词汇等，将课程内容上传小程序后台系统 英语能力：六级以上，有托福成绩、雅思成绩优先，英语、翻译相关专业优先 工作时间：9:30-18:30 工作日三天及以上 可实习三个月以上时间 要求在读</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>小程序</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2588,11 +2393,6 @@
           <t>工作职责:核心职责1.模型制作2.根据原画设计完成物件道具模型及场景建筑模型的制作3.按照规范优化模型拓扑结构及面数，修正模型光影信息4.合理分布UV最大化UV利用率5.在Unity引擎中搭建场景及道具与调整物体材质表现效果 工作要求:任职要求技能要求熟练使用Maya / 3ds Max / Substance Painter有一定的ZBrush雕刻能力了解PBR材质流程及三渲二风格专业能力扎实的美术基础，熟悉场景制作规范与流程有一定的空间结构、光影表现的理解能快速理解原画设计意图并落地执行加分项能够脱离原画自主优化场景及道具熟悉unity资产方面的模块投递需要作品集，作品集需包含：①单体模型（展示拓扑与UV）②场景案例（能有含引擎效果截图的最好）</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2635,9 +2435,6 @@
           <t>C、C++、Java、PHP、Python</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2670,15 +2467,11 @@
           <t>【岗位职责】 1. 参与头脑风暴提供创意想法，根据项目需求提出独特见解； 2. 根据脚本内容，完成段视频的素材收集、整理； 3. 完成于多媒体展项、品牌数字化、企业宣传等多种载体需求的视频后期的剪辑、特效、调色等包装工作。 【任职要求】 1. 影视制作、视觉设计等相关专业优先； 2. 熟练使用PR、PS、AI、AE等视频、图片编辑软件，能够独立完成视频的后期剪辑和简单的特效包装工作； 3. 思维活跃，富有创造力，具有优秀的沟通协作能力； 4. 热爱视频制作，喜欢观看不同的影视作品并且有个人见解。 【你将获得】 1. 对数字设计行业的全面认识，有机会参与大型展项的制作活动； 2. 专业设计师的指导，提高自身的软件应用能力和实用技能； 3. 获得清晰的职业规划和扎实的技能积累。</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2711,11 +2504,6 @@
           <t>1、负责抖音电商专业领域方向（如休闲零食、饮料冲调、粮油米面等）头部及潜力短视频作者的运营，负责作者关系的建立、维护和拓展，保持有效沟通。根据公司需求执行媒体推广方案，兼顾孵化数量与标杆案例影响力双目标； 2、探索专业领域作者电商成长路径，协同行业、营销、产品等团队优化经营效率与内容模式，打造垂类特色达人案例并沉淀方法论，推动同类型达人高效成长； 3、对接平台内外资源（活动、流量、政策），对GMV、垂类达人活跃度、内容种草转化率等核心指标负责，定期复盘优化策略，重点达人分层运营管理，结合抖音内容特性，制定行业策略、推动业务模式创新； 4、分析业务数据，设计与优化市场推广策略，完成标杆案例/方法论的挖掘与建立，通过策略设计与跨部门协作（产品、营销、规则等）提升运营效率，推动生态健康发展。</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2748,11 +2536,6 @@
           <t>提供转正机会，购买五险一金，转正月薪7-11K 薪资：150-300元/天； 要求：出勤5天/周，最低3个月，合适的话可以长期实习 优先研三或大四，研二大三不忙的也可以 【岗位职责】 1. 【产品开发】配合教研主编，编辑校对小学、初中语文课件、教材、试卷等资料； 2. 【产品优化】收集分析学情考情、教学反馈、市场竞品等信息，为产品优化迭代提供支持； 3. 【教学支持】配合教研主编，提供教师备课、上课、课后服务所需物料，参与师训、磨课等活动。 【任职要求】 1. 2026、2027届统招本科及以上优秀在校大学生，汉语言及相关专业优先； 2. 责任心强，自驱力强，做事细致入微，对教育事业有敬畏心； 3. 学习能力强，逻辑思维强，能迅速从新材料中提取有效信息； 4. 热爱教育事业，可长期实习者优先。</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2795,9 +2578,6 @@
           <t>Java、Linux、Python、Rust、数据分析</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2840,9 +2620,6 @@
           <t>Excel、NumPy、Pandas、Python、SQL、scikit-learn、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2885,9 +2662,6 @@
           <t>内容运营</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2930,9 +2704,6 @@
           <t>SQL</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2965,11 +2736,6 @@
           <t>1.负责在抖音平台筛选观看漫剧 2.与团队合作，确保内容发布的 高效和质量。 3.持续优化工作流程，时间自由。 任职要求 1.具备出色的沟通能力和执行能力，能够与团队成员有效协作 2.能在规定时间内完成上级交付的任务。 3.具有良好的团队合作精神，能够迅速适应团队环境</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3012,9 +2778,6 @@
           <t>PPT</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3047,15 +2810,11 @@
           <t>关于我们 博世集团（Bosch Group）成立于1886年，全称是罗伯特·博世有限公司（BOSCH），是工业技术、消费品和能源及建筑技术的产业。博世公司以其创新尖端的产品及系统解决方案闻名于世。 博世集团是全球第一大汽车技术供应商，员工人数超过 42万，遍布 50 多个国家。2022年销售额达到884亿欧元，其中在中国销售额达到1323亿人民币。 2018年7月19日，《世界500强排行榜发布，博世集团位列75位。2022年12月，位列《2022胡润世界500强》第58位。 岗位职责 支持品牌及视觉识别（VI）设计需求，包括设计系统展示、宣传物料设计等。 参与设计系统的搭建与维护，涵盖 UI 组件、图标、字体、视觉规范等。 设计、优化并输出可复用 UI 组件，保证一致性、易用性，并与开发无缝对接。 使用 Figma 完成 UI 元素设计，制定设计规范以支持项目落地。 编写设计文档与模板，推动设计系统在各团队的普及与应用。 参与 UX 研讨，优化设计流程，加强设计与开发团队协作。 任职要求 硕士学历优先。 视觉设计、数字媒体艺术、平面设计或相关专业背景。 拥有优质作品集，可体现 UI / 视觉设计能力与设计思维。 沟通与问题解决能力突出，具备良好团队协作能力。 扎实掌握以用户为中心的设计原则。 福利: 500强外企，跨文化交流，大平台新视野。 公司有食堂，工作氛围轻松愉快，可优先接</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>原型设计</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3088,11 +2847,6 @@
           <t>岗位职责： 1 、报道新车上市活动，试驾并撰写原创试车报告，车型导购文章。 2 、参加各大车展的报道工作，根据车型信息撰写相关的原创文章。 3 、参与相关专题策划和汽车类营销活动的执行，负责相关栏目的日常维护以及内容更新。 任职要求： 1 、人品端正，工作细致耐心，踏实肯干，吃苦耐劳。 2 、写作水平者优先考虑。 3 、专业不限，有驾照者优先考虑。</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3135,9 +2889,6 @@
           <t>Excel、人工智能、内容运营</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3170,11 +2921,6 @@
           <t>工作职责: 1.支持学堂日常宣传推广工作，主要负责宣传视频策划及拍摄制作、宣传照片拍摄、采访支持、部分文案撰写等。 2.负责微信公众号内容编辑与发布。 3.协助团队完成宣传活动的策划与执行。 4.学堂安排的其他工作。 任职资格: 1.统招本科或硕士在读，新媒体、新闻、传媒或相关文科专业。每周可实习4-5天 2.有过视频制作相关工作经验者优先考虑。 3.热爱摄影，具备较好的摄影、摄像技能，有较为丰富的视频制作经验。 4.具有较好的文字功底，能够根据要求撰写不同文体的文案。 5.领悟力、执行力强，同时做事严谨细致，有负责心。 6.希望通过实习获取经验，提升能力和眼界，能吃苦耐劳，愿意付出时间和精力到实习工作中。</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3207,15 +2953,11 @@
           <t>【岗位职责】 1、开展高端装备细分领域（智能制造、机器人、航空航天等）产业研究，参与研究报告的编写、市场调研等，整理和分析行业内最新动态和技术发展趋势； 2、协助产业研究员完成高端装备研究相关课题与项目； 3、协助团队完成高端装备产业战略规划、投资并购、产业论坛与资源对接等相关领域的工作。 【岗位要求】 （1）重点院校在读研究生及以上学历，要求实习时间至少3个月以上，每周实习3天以上（机械、控制、电子、航空航天等工科专业优先）； （2）热爱高端装备产业，熟悉产业研究的基本方法，具备较好的分析能力和敏锐的判断力； （3）具备良好的数据搜集、处理及报告写作能力，能够熟练使用Word，Excel、PPT以及其它金融数据分析类软件；</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Excel、PPT、Word、市场调研、数据分析</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3248,11 +2990,6 @@
           <t>中小学培训项目助理 简介： --公司长期为企业和中小学提供培训或工作坊，因学校项目需要招聘实习生，协助顾问或培训师开展培训工作的准备与交付。 工作内容： 初期： 1. 负责培训前的材料制作、场地布置、人员通知、物料采买、餐食订购等准备工作； 2. 在培训期间协助顾问做好人员接待、签到、拍照、餐饮、文档归类和场地整理等工作； 后期： 3. 对于想走专业路线的，可免费或优惠接受顾问的专业辅导，达到技能标准后可逐步参与培训项目的设计与更多交付工作； 4. 合作一定时段后，可成为长期事业合作伙伴。 人员要求： 1. 喜欢与人打交道，愿意支持他人学习和成长，并从中获得乐趣和成就； 2. 具备积极主动的服务意识，乐意为培训项目的实施提供创新建议和采取行动； 3. 对参与项目实施中涉及到的雇主方、客户方的商业信息保守秘密，不外出（根据项目需要，或许提前签署保密协议）； 4. 教育学、人力资源、心理学、中小学教育或教育管理等专业在校研究生优先。 劳动报酬： 1. 按日（含半日）支付劳动报酬，基本标准：150元/天，北京市内跟课/项目180元/天，京郊或外省市出差200元/天；提供午餐或餐补； 2. 每月1日支付上个月劳动报酬； 3. 为实习人员在实习期间购买保险。 工作地点： 1. 北京市内或全国，通常在客户指定的培训场所，如酒店或客户内部会议室； 2. 可以选择在北京市内或出差两种工作方式。 工</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3285,15 +3022,11 @@
           <t>【工作内容】 1、主要负责公司小红书和百家号等平台账号内容撰写，根据公司需求和定位逐渐输出有高度、有深度的优质传播性内容； 2、保持平台账号良好的互动，挖掘用户兴趣点增加粉丝数提高关注度，维护良好的互动氛围，增加粉丝粘性； 3、及时回复客户的问题，负责简单的客服工作。 【任职资格】 1、大专及以上学历，大三、大四在校生，不限专业、不限经验，新媒体、新闻传播、广播电视等相关专业优先考虑，有新媒体实习经验优先考虑； 2、对新媒体运营感兴趣，有一定的文案写作和数据分析能力，愿意主动学习和扩充个人知识面， 3、网感好，创意优，执行力强，有良好的策略思考能力并能独立撰写方案，能够做图片处理；熟悉ps/秀米/易企秀等； 4、知识面广，思维活跃，工作主动，有责任感，能承受较大的工作压力； 5、有良好团队合作精神和较强的执行力，具备独立思考能力、观察力和应变能力。</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>内容运营、数据分析</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3336,9 +3069,6 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3381,9 +3111,6 @@
           <t>Git、React、TypeScript</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3416,15 +3143,11 @@
           <t>职位亮点 独立设计项目，免费咖啡，世界五百强实习证明，免费健身房，导师直面进度快（最快一周内到岗)，行业前沿AI技术学习，超棒团队氛围 职位描述 实习周期：3个月及以上（超过3个月实习优先，每周全勤） 税前薪资：本科150元/天；硕士180元/天 你的工作将影响“未来” 作为联想上海未来中心的平面设计实习生，你将直面全球前沿科技展示场景，直面行业客户需求。 在这里，你将身处科技浪潮的前沿。 岗位职责 1.部门市场推广、日常业务所需的各类视觉（主KV设计、延展设计制作、视频剪辑等）需求输出（50%） 2.协助对接供应商，就视觉需求进行前期沟通并跟进进度，把控效果（30%） 3.部门其他例如拍摄等支持工作（20%） 注: 1.请在简历中附上作品集 2.线上面试，通过初面有笔试环节 3.掌握一定摄影基础 投递要求 简历要求：不限 截止日期：长期可投递</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3457,15 +3180,11 @@
           <t>岗位职责 1、为库洛周边提供富有创意的想法和赋予其实现的可能性； 2、负责衍生品设计，包括并不仅限于产品或者包装设计； 3、完成导师交代的其它设计任务。 岗位要求 1、本科及以上学历，有游戏周边设计相关经验优先； 2、熟悉平面设计常用软件包括但不限于PS、AI、SAI等； 3、熟悉主流二次元产品，战双或者鸣潮资深体验者优先。</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3508,9 +3227,6 @@
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3543,15 +3259,11 @@
           <t>1、负责快手各产品、系统的Web前端研发； 2、负责快手各产品、系统的易用性改进和界面技术优化； 3、参与前端前沿技术研究和新技术调研。</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3594,9 +3306,6 @@
           <t>Excel、PPT、办公软件</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3639,9 +3348,6 @@
           <t>Excel、Word、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3674,15 +3380,11 @@
           <t>Role Summary The ERP Intern will support the ERP team in daily operations, system implementation, and optimization initiatives. This role provides hands-on exposure to ERP systems, business processes, and cross-functional collaboration, especially within finance, supply chain, and IT-related functions. The intern will work closely with ERP project members and business stakeholders to support system data, documentation, testing, and reporting activities. Key Responsibilities Support ERP project teams in daily operational and project-related activities Assist in ERP system data preparation, data</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Excel、Oracle、PPT、Power BI、办公软件</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3715,11 +3417,6 @@
           <t>1、公关、网红营销：由导师指导，通过各种平台和渠道挖掘和招募与品牌形象契合的有潜力的行业红人(Facebook/Instagram/Youtube/Tiktok等）及行业媒体并达成合作；对接、跟进、管理PR及红人营销进展；回收、分析数据并进行优化，不断为网站引流，提高产品曝光和品牌知名度，同时促进销售转化。 2、用户运营：由导师指导，对用户社区进行维护，促进新用户加入，与留存用户沟通，挖掘用户需求，保持社区活跃；与社媒和内容营销联动，举办社区活动；对日常数据进行统计、分析。 3、网盟营销：在既定的网盟平台上，触达、管理媒体资源；收集、回顾数据；优化媒体策略；调整媒体素材，并参与与客户之间的对接。 4、导师交办的其他营销工作 任职资格： 1、做事细心、勤恳，好学、善于找寻案例学习研究并用于实操，能沉下心研究数据和转化链路，接受上级指导； 2、性格开朗，善于沟通，执行力佳且有责任心； 3、对跨境营销有兴趣，有志于在跨境营销方向长期发展； 4、优秀的英语读写能力，海外留学或工作经验优先，英语专业优先； 5、本科学历以上，具备营销经验者优先。</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3752,15 +3449,11 @@
           <t>岗位职责（具体工作内容） 1.负责国际收单、钱包等场景的支付风险识别&amp;决策模型的选型、开发和优化，负责模型部署应用、维护、监控和升级迭代; 2.深入理解国际支付业务和风险，总结和提炼用户行为序列等风险特征，并对特征挖掘结果进行评估和验证; 3.负责建模流程优化，提升模型开发和部署效率，降低模型维护成本; 4.基于图算法、时序算法等对用户风险进行识别，在小样本、无样本场景上能够通过无监督、半监督、元学习等算法对风险进行有效识别。 5.研究前沿机器学习算法在支付风控领域的实践和应用。 任职资格（学历、目标院校、语言、技能、性格等要求） 1.计算机、数学、统计学等专业本科及以上在读，有海外留学经历者加分，具备一定基础的英语交流能力; 2.熟练掌握Pytorch等建模语言和数据挖掘工具, 熟练掌握数据挖掘、机器学习、深度学习等方向理论和应用方法; 3.突出的分析问题、解决问题和动手实践的能力。自我驱动，具有较强的学习能力、创新应用能力、以及沟通协调能力; 4.有相关工作经历和论文者加分。</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>PyTorch、数据挖掘、机器学习、模型部署、深度学习</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3793,15 +3486,11 @@
           <t>岗位职责： 1、用户增长与转化:制定并执行用户增长策略,关注从内容曝光到最终交易转化的完整全链路,通过A/B测试等手段优化转化率； 2、内容策划与营销:结合市场热点(如财报季、美联储会议、CFI等)、用户生命周期策划高转化活动,提升用户交易意愿 3、产品力包装:针对不同市场行情(如期权、IPO、特定品类)包装产品品优势,将其转化为具体的营销计划 4、熟悉目标客群画像、痛点和诉求,基于数据分析拆解用户行为路径增长策略迭代,对运营内容、手段和渗透场景持续优化 5、跨部门协同:与总部研发、设计、用研团队配合,确保增长策略与产品特性及市场需求高度契合 任职要求 1、具备互联网增长思维,能够通过数据分析驱动决策 2、优秀的文案功底和独立内容策划能力 3、具有良好的逻辑思维能力和数据分析能力 4、具有较强的团队合作意识,良好的沟通表达能力,善于跨团队合作调动多方资源 5、具有快速学习能力、独立主动思考能力和抗压能力 6、如有一定的美股投资(炒股)经验者加分 7、一周出勤五天,最少实习三个月,表现突出者可有转正机会。 8、语言要求:泰语母语、英语听说读写流利,中文加分 9、专业要求:金融、经济及相关专业；本科及以上学历优先。</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>数据分析、渗透测试、用户研究</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3834,11 +3523,6 @@
           <t>岗位职责: 1、协助交易指令执行操作，开展执行情况监控和及时反馈异常； 2、协助相关系统需求分析、业务测试等工作； 3、协助交易业务相关数据统计、分析； 4、公司交付的其他工作。 任职要求: 1、硕士研究生以上学历在校学生； 2、工作认真细致，具备较好的沟通协调能力、具备一定抗压和多线程工作能力； 3、具备证券从业、期货从业、基金从业资格优先。</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3871,15 +3555,11 @@
           <t>岗位职责（具体工作内容） 1. 算法研发辅助工作。协助算法工程师开展自动驾驶红绿灯感知领域深度学习算法的研究与开发，聚焦计算机视觉方向，深度参与图像检测与分类、目标跟踪等核心任务。在工程师指导下，进行模型的架构设计、代码实现与迭代优化，将理论知识转化为实际的算法解决方案，为自动驾驶系统的环境感知能力提升提供技术支持。 2. 数据处理与模型训练。负责自动驾驶场景下各类数据的处理工作，完成数据的清洗、标注与预处理，构建高质量的训练数据集，保障数据的准确性与多样性。参与模型训练全流程，根据训练结果调整参数，优化模型性能，提升目标检测的精度与跟踪的稳定性。 3. 技术调研与知识沉淀。持续跟踪深度学习在自动驾驶领域的前沿技术动态，包括新型算法架构、先进的训练策略等。定期整理调研成果，形成技术文档并在团队内部分享，促进团队技术水平的共同提升。同时，协助撰写算法研发过程中的技术文档，沉淀项目经验与技术细节，保障研发流程的可追溯性。 任职资格（学历、目标院校、语言、技能、性格等要求） 1. 专业与学历。要求本科及以上学历，计算机科学与技术、软件工程、自动化、电子信息工程等相关专业在读。具备扎实的计算机基础知识，熟练掌握Python、C++等至少一种编程语言，熟悉深度学习框架如PyTorch、TensorFlow等。 2. 深度学习知识储备。掌握深度学习的基本原理，熟悉CNN、RNN、Transfo</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>PyTorch、Python、TensorFlow、深度学习、计算机视觉</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3912,15 +3592,11 @@
           <t>1、协助各业务线技术与资源解决方案工程师，做需求分析与解决方案设计； 2、协助各业务线技术与资源解决方案工程师，做各业务线的资源交付； 3、协助各业务线技术与资源解决方案工程师，做业务数据的统计与分析。</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3963,9 +3639,6 @@
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4008,9 +3681,6 @@
           <t>PPT、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4043,15 +3713,11 @@
           <t>该岗位为校招实习岗位，有明确转正机会！需连续实习至少2个月，实习入职时间灵活！ 您可以： 1. 参与游戏研发管线AI应用的全栈开发，将大模型能力转化为极致的用户体验，如AI绘图、AI代码、ChatBI、LLMs应用等； 2. 构建高并发、低延迟的AI服务架构，优化推理性能与成本； 3. 设计并实现AI Native的产品交互，探索人机协作的新范式； 4. 开发AI应用的基础设施，包括 agent 套件、模型测评、模型路由等。 1.本科及以上学历; 2.熟练掌握C++的使用，熟悉Python/Golang/C#优先； 3.熟练掌握常用数据结构与算法； 4.熟悉分布式系统设计、操作系统、网络编程等； 6.良好的代码风格和编程习惯； 7.自主学习能力强，善于沟通，有团队合作精神，乐于分享。</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Go、Python、人工智能、全栈、大模型</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4084,15 +3750,11 @@
           <t>1、能够熟练通过公开信息收集，用户调研，专家访谈等研究方法进行深入细致的行业分析，为公司业务发展方向提供支持； 2、与业务团队紧密合作，基于内部分析及外部竞对和市场调研，产出策略建议并推进落地执行； 3、 结合业务跟踪和业务理解，形成专题分析课题，独立分析得到业务认知，并推动业务策略落地。1、本科及以上学历，有过互联网行业分析、商业分析、战略分析等相关实习经验，熟悉互联网常见的分析方法论； 2、具备优秀的框架化思维能力，能够运用逻辑分析能力将复杂问题分解、验证并形成结论； 3、良好的沟通协调、推动决策落地能力，通过分析驱动业务发展。</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>市场调研、用户研究</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4125,11 +3787,6 @@
           <t>岗位职责： 1.根据品牌调性和产品特点，撰写优质小红书笔记， 2.关注小红书平台热点话题，结合产品特点进行内容创作。 职位要求： 1.在校大学生，媒体、设计、广告、中文等相关专业优先。 2. 做过旅游类的优先！！（打招呼的时候可以提一下你做过）；需要会用ins并且我们需要会作图的编辑者，会醒图、稿定设计、可画、ps等作图软件。 3. 具有较好的网感，喜欢网上冲浪，熟悉小红书社区文化和用户喜好。 4. 具备良好的文字功底和审美能力、做图能力，能够独立完成内容创作。 5. 工作认真负责，具备良好的沟通能力和团队合作精神 工作时间：灵活的工作时间，线上办公，按照要求完成稿子即可 工资待遇：按篇结算（月结），优质内容额外奖励，多劳多得。</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4162,15 +3819,11 @@
           <t>1、负责通过基于大语言模型及多模态大模型的微调、prompts调优、指令构建及演化技术，将大模型的生成、理解、交互能力在公司核心业务场景应用落地，包括但不限于AIGC创意生成、视频处理、智能化特效、智能对话、代码生成、音视频传输、电商场景内容理解等； 2、负责LLM及多模态大模型的应用中台及相关技术模块搭建，包括但不限于Agents 、RAG、 function call、system prompts等，探索大模型应用前沿及新兴应用场景； 3、跟踪行业及大模型技术发展，结合业界前沿技术和业务需求，打造大模型应用的最佳实践； 4、了解业务，与公司各技术团队密切配合，能与产品、运营等角色高效沟通需求和目标，发挥自己的主观能动性，设计技术解决方案，培养自己的良好的业务sense和综合素质。</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>AIGC、RAG、人工智能、多模态、大模型、微调</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4203,15 +3856,11 @@
           <t>【岗位职责】 1.制定用户增长及留存策略，跟进方案落地及效果监测 2.根据全年市场热点，协助完成运营活动策划及执行落地 3.负责协助业务的日常运营工作 4.岗位兼具产品运营、产品经理职责 5.方向涉及航旅纵横app具体业务：酒店、保险、社交、用车等 【任职条件】 1.统招本科、硕士在校生，统计学、计算机相关专业优先 2.每周至少实习4天，持续实习3个月及以上 3.优秀的逻辑思维、结构化思维能力、表达能力，对问题能进行结构性分析并制定解决方案 4.较强的主动性、学习能力、有较强的抗压能力和执行力 5.擅长SQL者优先</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>SQL、用户研究</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4244,11 +3893,6 @@
           <t>工作职责： - 负责维护和管理公司私域社群及用户，包括但不限于企微群、企微小程序、公众号等，建立和维护良好的用户关系。 - 负责客户的咨询和提问，解答各类问题，并协助客户解决问题。 - 收集用户反馈信息，协助团队进行产品的改进和升级。 - 负责私域小程序的内容审查和整理，确保内容的准确性与时效性。 - 紧密合作团队成员，为用户提供最优质的服务。 任职要求： - 本科及以上学历。 - 具备良好的写作能力和语言表达能力。 - 具备心细、积极主动、团队合作精神和较强的沟通能力。 - 有较强的责任心，能积极响应公司安排和安排自己的任务。 - 有社交媒体运营和客户服务经验或相关实习经历者优先。</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4281,15 +3925,11 @@
           <t>岗位职责（具体工作内容） 1、策略执行与效果闭环：协同营销策略设计、配置审核及上线全流程，监控核心指标，完成效果归因与复盘，直接驱动策略迭代。 2、用户心智建设：基于数据分析，定位用户认知缺口，策划并执行宣教内容，通过多渠道触达，提升关键功能的用户渗透与留存。 3、需求推进与协同：作为业务方与产研团队的“连接器”，承接并梳理小型需求，推动需求从评审到上线的全链路。 4、数据分析与监控：完成对业务关键指标的监控及异常波动的判断，主动思考、反馈数据发现的各类问题，参与兜底方案配置与流程优化，为业务安全护航。 任职资格（学历、目标院校、语言、技能、性格等要求） 1、实习一周4天及以上，至少连续3个月，优先考虑能尽早入职的候选人； 2、本科及以上，专业不限，数据分析、统计学、数学相关专业优先； 3、具备较强的数据分析能力， 熟练掌握Excel和SQL（必须项），有A/B Test经验加分，有看板搭建能力经验加分； 4、具备较强的快速学习能力，细心且责任心强，有较好的逻辑分析能力。 5、出色的沟通与协同能力，能清晰表达、高效对齐，并具备优秀的文档习惯。 6、对用户和业务有强烈的好奇心与洞察欲，自驱力强，能在快速迭代中保持专注，对结果负责。</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Excel、SQL、数据分析、渗透测试</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4322,11 +3962,6 @@
           <t>Alicat为全球知名的流量计、流量控制器、压力计、压力控制器的制造商。艾里卡特科技有限公司(Alicat Scientific Inc.)于1991 年在美国成立，隶属于英国豪迈(Halma)集团环境与分析事业部，致力于为实验科研、环境监测、生物制药、检测分析、燃料电池、食品饮料等行业客户提供快捷、精准、稳定的质量流量和压力测控解决方案。 Alicat大多数产品采用独特的内部补偿型层流差压技术，利用泊肃叶定律，并依托精密的机械制作工艺及先进的电子技术，来进行补偿因压力和温度引起的体积流量和质量流量间的差异，对用户标准工况进行修正，可以精确测量出介质的质量流量、体积流量、压力和温度。 1. Learn Alicat products and their working principles, and provide basic technical support to customers, including technical Q&amp;A and operation guidance. 学习 Alicat 产品及其工作原理，并为客户提供基础技术支持，包括技术问题解答和操作指导。 2. Conduct product testing and basic troubleshooting for internal teams and customers, and provide clear</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4359,15 +3994,11 @@
           <t>职位诱惑：发展空间大、岗位晋升、带薪年假、周末双休职位描述： 工作职责： 1. 负责前端界面的开发及制作，以及前端与业务层交互开发和维护； 2. 具备良好沟通能力，配合产品、设计、后端完成项目； 3. 持续的优化前端体验和页面响应速度，优化代码并保持良好兼容性，提升web界面的友好和易用； 4. 具备较强的责任心，积极完成分解到个人的工作，保质保量，并及时反馈工作进度； 上岗要求： 1. 掌握JS、Html、Css等前端技术，对es6、es7规范有一定了解。 2. 了解Vue框架、并接触使用过uniapp，根据设计稿完成页面实现。 3. 熟练使用VSCode、Git代码编辑、管理工具</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Git、JavaScript、Vue、前端、后端、小程序</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4410,9 +4041,6 @@
           <t>SQL、大数据</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4445,15 +4073,11 @@
           <t>[新加坡公民/永居/持有Studentpass优先考虑，日薪150新币左右] 工作职责 -负责协助广告系统策略设计和算法优化 -协助支持广告竞价机制设计和实现 -协助支持广告模型CTR和CVR预估 -协助支持广告系统先进技术研究 -协助探索大模型在广告系统上的应用 任职资格 -可以实习4个月以上，每周出勤4-5天 -硕士及以上学历，数学、计算机等相关专业 -较优秀的编程和算法能力，熟悉python编程语言、熟悉Linux开发环境、熟悉Spark、熟悉常的数据结构和编程算法者优先 -了解统计学习、深度学习理论基础，有相关研究成果或发表过论文者优先 -具备较优秀的分析和解决问题的能力，对解决具有挑战的问题充满激情，具备良好的主动性和求知欲、具备良好的沟通协作和抗压能力</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Linux、Python、Spark、大模型、深度学习</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4486,15 +4110,11 @@
           <t>areparcel 是一个聚焦20世纪经典中古与当代艺术家居的复合品牌，提供以艺术软装驱动的豪宅全案设计、空间策展与美学收藏顾问服务。art redefine essential 是我们的品牌哲学。 *请提前在社交媒体搜索并对areparcel有初步了解 *递交不大于20M的基本简历与作品集（项目案例） *硬性要求：会室内设计相关软件 *可直接私信沟通，请在私信中简单分享： 你眼中的 areparcel，以及你欣赏的 3 个家具品牌或室内设计工作室，并说明原因。 我们正在寻找一位希望进入室内 / 软装行业的设计实习生，参与真实设计项目与展厅日常运营。这是一个复合型岗位，你将同时接触艺术豪宅设计项目流程与进口家具行业的实际运作。 工作内容： 设计项目相关 * 跟随设计师进行现场量房与空间记录 * 使用 AutoCAD 绘制平面图、立面图及基础施工图 * 协助整理项目资料、图纸与清单 * 协助软装方案资料收集与整理 展厅与日常运营 * 展厅接待与基础讲解 * 家具与空间相关图片 / 视频拍摄协助 * 参与家具/家居相关展览项目的灵感收集、创意构想 * 协助展览落地、展厅陈列及相关准备工作 * 协助处理日常运营与现场事务 当没有设计项目时，将以展厅与内容工作为主。 基本能力要求： * 室内设计 / 环境艺术 / 建筑相关专业优先 * 熟练使用 AutoCAD，SketchUp，Photo</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4527,15 +4147,11 @@
           <t>岗位职责（具体工作内容） 1、协助团队进行大模型相关数据的收集、清洗与标注工作，确保数据质量符合模型训练要求，参与数据预处理流程的优化辅助。​ 2、支持大模型训练过程中的基础监控，如记录训练日志、整理训练过程中的关键指标变化，协助分析训练过程中出现的简单问题。​ 3、参与大模型相关文档的整理与归纳，包括技术文档、测试报告等，协助搭建和维护团队知识库。​ 4、辅助进行大模型的简单测试工作，如执行预设的测试用例，记录测试结果，反馈模型在特定场景下的表现。​ 任职资格（学历、目标院校、语言、技能、性格等要求） 1、在读本科及以上学历，计算机科学、人工智能、数据科学、数学等相关专业优先。​ 2、对 AI 大模型技术有浓厚兴趣，了解大模型的基本概念和工作原理者优先。​ 3、具备一定的编程基础，熟悉 Python 语言，了解常见的数据处理库（如 Pandas、Numpy）者优先。​ 4、具备良好的逻辑思维能力和学习能力，能够快速理解和掌握新的技术知识。 5、每周可实习5天，实习周期不少于 6 个月；能遵守用户信息保密规范。</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>NumPy、Pandas、Python、人工智能、单元测试、大模型、数据科学</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4578,9 +4194,6 @@
           <t>C、C++、Java、Kotlin、Swift</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4613,15 +4226,11 @@
           <t>-协助根据业务发展需求，开展针对各细分赛道和行业的研究分析工作，包括整体市场环境、细分领域发展、竞争对手分析、新商业模式探索、新技术研究等，形成具有前瞻性的观点和报告，为业务发展提供战略分析和建议 -协助某一细分业务的顶层规划设计，包括整体战略目标设定、战略路径拆解、组织设计和定位、基础设施建设等，拆解目标并对目标进行跟踪、管理、监督，及时给出切实建议，确保战略落地和目标达成 -协助重点项目推进，及时跟进业务需求，做好内外部资源协调，确保项目顺利完成 -协助不断探索新机会，研究潜力市场与创新玩法，为业务发展提供新机遇线索 任职资格 -具备扎实的市场研究和策略分析能力，具备良好的信息获取、报告整理与分析能力 -熟练使用Excel、PPT，能够独立完成分析任务 -战略分析、商业分析、投研分析等相关实习经验 -有头部咨询公司实习优先、头部互联网公司战略/商分实习优先</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Excel、PPT</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4654,15 +4263,11 @@
           <t>⛳️你将做什么 1. 海外创作者挖掘与建联：使用 AI 工具在 Instagram、TikTok、YouTube 等平台批量挖掘高质量创作者，建立达人数据库并主动触达； 2. Cold Outreach：设计并执行高转化率的邮件/DM 触达链路，推动创作者和品牌方注册产品； 3. 用户增长与用户分层：制定并执行用户增长策略，根据用户行为与价值进行分层运营，提升用户活跃度、留存与转化； 4. 数据驱动增长：追踪转化漏斗各环节数据，持续复盘优化增长策略，用数据说话而不是凭感觉。 ? 我们希望你是 1. 本科及以上在读或应届（2026届），可实习≥3个月，每周≥4天；线下实习 2. 英语能力过硬，能独立完成英文 Cold Email、社媒内容撰写和用户沟通； 3. 熟悉海外主流社媒平台（Instagram / TikTok / YouTube / Discord）的内容生态，是资深用户，懂创作者在想什么； 4. 有数据意识，愿意基于结果调整策略，不只是「产出内容」而是「驱动增长」； 5. AI 重度玩家——ChatGPT / Claude / Gemini 是你的日常工具，不是新鲜玩具。 加分项 1. 有出海 APP 或 SaaS 产品的海外运营/增长经验； 2. 有 Cold Outreach 实战经验（邮件、DM、社群拉新等）； 3. 了解 n8n / Coze / Make 等自动</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>人工智能、大模型、用户研究</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4705,9 +4310,6 @@
           <t>Excel、PPT、Word、办公软件</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4750,9 +4352,6 @@
           <t>PPT</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4785,11 +4384,6 @@
           <t>1.协助营运总监处理日常管理事务，传达上级指令并监督终端执行，定期提交营运分析报告。 2.统筹分店营业区域运作，制定销售、毛利计划并跟进落实，监控经营指标完成情况。 3.负责商场巡场检查，协调租户关系、催缴租金，处理顾客投诉与突发事件。 4.汇总销售数据，分析商品结构并提出调整建议，参与库存管理与盘点工作。 5.起草自营区域管理制度，审查员工业绩考评，向经理提人员定编建议。</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4822,11 +4416,6 @@
           <t>岗位职责: 1. 参与协助投资项目评审、尽职调查与项目执行； 2. 收集整理行业及标的公司相关的信息； 3. 协助进行医疗医药行业投资研究； 4. 基金运营等方面的工作。 任职要求: 1. 诚信正直、低调谦逊、艰苦奋斗，具备良好的道德品质； 2. 国内外院校大三及以上在校生； 3. 具有生物医药相关行业工作或实习经验者优先； 4. 具有券商/投资/咨询等实习经验（不限行业）者优先； 5. 具备良好思考能力、抗压能力，对投研有浓厚兴趣，有专业研究成果者优先； 6. 每周实习时间4天及以上，至少3个月，6个月以上者优先。</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4859,11 +4448,6 @@
           <t>职位描述 1、内容营销：协助执行游戏版本传播，对接内部部门及外部供应商，主动跟进进度； 2、创意产出：利用对游戏行业及各社交媒体平台的了解，产出有话题度和看点的创意； 3、营销传播：协助版本推广、节点传播等游戏营销传播工作； 4、协助处理部门日常基础性工作，例如商务合同跟进等。 职位要求 1、本科及以上学历，专业不限；2025届及以后毕业的同学 2、保证一周4-5天的工作时间； 3、出众的沟通能力，良好的审美及文字表达能力，良好的执行力，积极乐观的心态； 4、熟悉竞技类、动作类游戏者加分，熟悉抖音、B站、小红书等平台加分； 5、投递岗位需附上游戏经历。</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4896,15 +4480,11 @@
           <t>工作职责:1. 参与游戏项目的开发与维护，协助完成游戏功能模块的设计与实现2. 使用UE5引擎进行逻辑开发，包括但不限于游戏玩法、UI交互、系统功能等3. 根据需求编写高效、规范的代码（C/C++/C#/Python），优化游戏性能与逻辑流程4. 协助团队进行游戏测试、bug修复及版本迭代工作5. 参与工具开发或脚本编写（如Python），提升团队开发效率6. 与策划、美术、程序等团队成员紧密协作，确保开发进度与质量7. 学习并掌握UE5相关技术文档，持续优化个人技术能力工作要求:1. 至少熟练掌握C/C++/C#中的一种，了解Python/LUA/Angel Script为加分项2.熟悉UE5引擎的基本操作，有实际项目经验者优先3.了解游戏开发流程，熟悉面向对象编程思想与数据结构4.良好的代码习惯：注重代码可读性、模块化设计、版本控制（如Git）与注释规范5.熟练使用AI编程辅助工具</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>C、C#、C++、Git、Python、人工智能</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4937,11 +4517,6 @@
           <t>岗位职责 1）负责实现Unity常见Shader效果 2）负责完善并优化灯光，阴影和体积雾效果 3）负责修改接入插件或开源项目 4）负责沟通美术与策划，把控最终美术效果的一致性和风格化 岗位要求 1）了解美术理论，具备优秀的游戏、电影、动画美术审美 2）了解计算机图形学，了解光栅化渲染，PBR和NPR，实时环境光渲染等基础内容 3）了解Unity美术相关管线，后处理和RenderFeature 4）具有游戏开发实操经验,比如参加GameJam,完成学校项目,完成小型独立游戏 加分项： 1）有自身的游戏作品集 2）参加过3个以上的GameJam 3）有写过实时光追实现或者GPU粒子，体素渲染等深入技术 4）有3D建模，打光和动画的作品集，展示了你的审美也ok</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4984,9 +4559,6 @@
           <t>Excel、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5029,9 +4601,6 @@
           <t>Agent、C、C++、Python、人工智能、大模型、强化学习、微调</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5074,9 +4643,6 @@
           <t>C、C++、Java、Swift、移动开发</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5109,11 +4675,6 @@
           <t>工作内容： 1、负责医疗知识类短视频的拍摄和剪辑，参与短视频账号日常运营 任职要求： 1、在校生，大专及以上学历，数字媒体、设计、广告、传媒等相关专业优先 2、熟练使用剪映/PR/AE等剪辑工具，有相关作品 3、善于学习，细致有耐心，积极主动，具备一定的审美能力 4、每周至少可现场实习4天，实习最少3个月</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5146,11 +4707,6 @@
           <t>岗位职责： 1.负责学校内智慧树网的智慧教室的日常巡视 2.智慧树网平台校内使用的指导和答疑 3.远程协助完成校内产品的问题定位，版本升级等 任职要求： 1.学习计算机，网络通信等相关专业 2.在校空余时间较多可控 3.本校的在校学生山东农业大学(岱宗校区)</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5183,11 +4739,6 @@
           <t>岗位职责 1.协助客服团队处理客户订单相关事物，包括订单确认，修改及提供单号。 岗位要求 1.需熟练掌握拼多多，淘宝，京东等购物软件，打字速度不能太慢 2.工作时间为9：00----18：00。 3.完成上级领导交办的工作事项 4.工作简单易上手，需有耐心不浮躁</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5220,15 +4771,11 @@
           <t>工作职责 1、围绕部门各业务模块搭建数据分析体系，动态监控各项业务指标。 2、快速理解业务需求，从客户运营视角通过大数据平台解决常见数据分析问题，形成数据分析报告以支持业务决策。 3、基于大模型能力，搭建AI Agent，完成会话质量分析，并形成优化建议。 4、协助完成配置类工作，包括触达配置、AI配置、业务系统配置等； 岗位要求 熟练使用AI工具，有一定的数据背景，熟练使用SQL、Excel办公软件 对数据敏感、对用户运营有兴趣；有较强的学习能力，沟通协调能力</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>Agent、Excel、SQL、人工智能、办公软件、大数据、大模型、数据分析</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5261,11 +4808,6 @@
           <t>你的工作内容： 1. "桥中”创始人IP_视频号+抖音的运营； 2. 选题产出：根据IP定位以及商业号特性，结合企业最新信息和短视频平台流行趋势，针对to B用户的选题内容的构思； 3. 内容产出：根据最终选题完成视频剪辑输出，进行视频脚本、拍摄（团队协助）、剪辑，可看往期的内容做一个初步了解； 4. 每日监控账号数据情况：快速复盘内容效果，敏锐捕捉热点与趋势，为视频产出策略调整提供一线依据。</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5298,15 +4840,11 @@
           <t>1、主要负责回森APP的特效设计工作，能够完成2D直播礼物的策划、动效设计。要求对直播礼物的设计、主题、镜头衔接、节奏感、音乐等方面有较好的把握； 2、熟练使用AI工具生成图片及视频。在工作中，能够依赖AI工具提升效率，熟悉AI工具的应用方式； 3、参与设计讨论，与产品、开发配合跟进特效细节的落地，在设计中积累沉淀，形成设计方法论，提升工作效率； 4、结合本领域的设计知识，掌握时下设计趋势，有较强的敏感度，参与前瞻性的视频创意设计和动态DEMO实现。 任职要求 1、AE是频繁应用的软件，必须熟练使用AE中基础动画、特效、粒子、插件等功能模块，2027届毕业生，数字媒体、美术设计、动画、影视等相关专业优先； 2、热爱AIGC和短视频领域，具备优秀的创新能力及设计审美； 3、良好的沟通能力和团队合作精神，思维活跃，对工作有责任感和自驱力，积极主动的学习能力。</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>AIGC、人工智能</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5349,9 +4887,6 @@
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5394,9 +4929,6 @@
           <t>Excel、PPT</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5429,15 +4961,11 @@
           <t>【核心职责】 内容编写：参与有声演播课程大纲设计，总结提炼教学重点和并完成文字内容产出。 素材开发：有一定的文学素养，能改编练习文本（小说/广播剧/散文），产出文字稿件。 教学辅助：录制课程的对比样音（正确与错误示范），制作教学课件。 竞品分析：拆解市面热门音频产品，输出演播风格与教学逻辑的调研报告。 【岗位要求】 专业功底：播音、表演、编导或文学类专业；普通话二甲及以上，文字功底良好。 教研思维：能将复杂的演播技巧（如对象感、气声运用）通俗化表达。 审美力：有声书/广播剧深度受众，能敏锐辨别声音质量与情感逻辑。有良好的视觉审美，能够产出内容清晰、格式统一、排版精美的PPT。 技能加持：熟练使用AU/剪映/PS及办公软件（PPT/思维导图）。 【加分项】 拥有成熟的音频作品或教育类自媒体运营经验。 会使用AI工具搭建工作流，快速提效。</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>PPT、人工智能、办公软件、市场调研</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5480,9 +5008,6 @@
           <t>计算机视觉</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5515,15 +5040,11 @@
           <t>1、负责游戏客户端模块功能开发、编辑器开发、功能迭代和线上维护； 2、按照产品设计要求，与团队其他人员一起协作，完成产品相关功能的开发。</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5566,9 +5087,6 @@
           <t>Excel、SQL、数据分析、数据可视化</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5601,15 +5119,11 @@
           <t>需要你 1. 多渠道商品基础运营：负责美团、饿了么、京东闪购、京东到家（新增）渠道商品全生命周期管理，承接上下架及素材更新需求，按规范在3个系统完成重复操作；定期开展在架商品异常排查、清单盘点，保障商品合规在线； 2. 商品信息与功能优化：维护日常/紧急客诉素材，整改平台商品审核失败问题；参与RPA及商家后台产品功能优化，对接IT部门推进饿了么、京东到家自动化上架落地，协调多渠道系统SOP差异与执行卡点； 3. 选品与质量分提升：聚焦爆品项目与平台会场需求，基于屈臣氏货品分类体系及渠道属性，开展精细化选品；持续优化多渠道商品质量分，提升商品曝光与转化效率； 4. 数据与库存管理：整理BO报表、收集商家后台数据，完成档期库存预估；汇总3个到家渠道商品流量数据，支撑品类分析、项目分析，协助推进数据看板落地； 5. 店铺运营与项目支持：负责店铺视觉更换、优惠券配置、新开门店首页装修及初期运营设置，整理sug词；协助项目PM完成数据整理、分析及选品相关辅助工作。 · 希望你 1. 本科及以上在读，市场营销、电子商务、零售管理等相关专业优先； 2. 熟悉美团、饿了么、京东闪购/京东到家等到家平台业务逻辑者优先，了解快消行业或屈臣氏货品体系更佳； 3. 具备较强的数据整理与分析能力，熟练使用Excel（Vlookup、数据透视表等），能高效处理多渠道数据汇总工作； 4. 沟通协调能力突出，可快</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Excel、数据运营</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5642,11 +5156,6 @@
           <t>岗位职责 1. 推文排版：公众号、小红书等平台推文视觉优化，提升传播力。 2. 海报设计：制作公益活动海报/宣传物料，嵌入二维码等互动元素。 3. 品牌维护：统一多项目视觉输出（LOGO、字体、色彩）。 岗位要求 1. 技能：熟练使用设计工具（PS/AI/Canva等），熟悉新媒体视觉风格。 2. 公益心：认同教育公平理念，能理解儿童阅读需求。 3. 协作力：支持远程协作，按时响应需求。 服务详情 - 地点：**线上为主**（云南志愿者可线下参与）。 - 时间：灵活工时，配合项目周期。 福利 - 上海志愿者证书 - 加入读书会，结识志同道合的朋友</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5679,11 +5188,6 @@
           <t>交易猫语音呼入客服 本岗位没有任何销售性质 不用外呼 工作比较轻松 公司主要做交易猫业务的，交易猫是阿里巴巴旗下的游戏交易平台 目前公司在职员工250+ 语音接听平台用户,及时有效的解答和指导用户在使用过程中遇到的疑问，根据知识库提供的标准化答复口径，及解决流程给予正确引导解决 ,如具体操作使用、功能解读等，同时受理不同渠道用户的咨询与投诉，安抚用户情绪，正确判断定位用户问题,记录用户信息及投诉内容，并进行适当解释和安抚，及时将投诉升级给投诉处理部门 招聘要求 ： 1、18岁以上，男女不限，大专及以上学历（条件优秀者放宽至高中）； 2、有客服经验的优先； 3普通话标准，性格开朗 综合薪资 3500-5000+ 五险 员工生日会 节假日福利 工作时间：08:00-23:00之间排班每个班次9个小时包含吃饭休息时间 没有通宵班 工作地点 现代光谷世贸中心C座3楼整层公司自购办公场地</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5716,11 +5220,6 @@
           <t>职责描述： 1. 每日整理需发函的用户清单，独立完成函件起草校对、用印申请、归档及分发，确保时效与准确性； 2. 负责对接法务和律所，对接诉讼材料准备和用印； 3. 负责业务数据整理。 任职要求： 1.本科及以上学历，在校生，专业不限； 2.细心严谨，有较强的责任心和沟通协作能力； 3.每周出勤不少于3天，实习6个月。</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5753,15 +5252,11 @@
           <t>1、根据不同应用场景（推荐、增长裂变、热点功能等）提出产品策略方案，推动具体策略的迭代升级及产品化功能落地，提升用户此功能的使用体验； 2、深入了解业务场景，通过用户调研、数据分析挖掘用户需求，基于用户反馈和数据分析，进行效果评估并提出产品改进点，不断迭代产品功能； 3、收集内外部需求，跟踪行业竞品动态，挖掘新的策略优化点并提出切实可行的产品方案； 4、通过用户调研、竞品分析、数据分析，学习和了解业界最新动态，发现产品机会点。</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>产品设计、市场调研、数据分析、用户研究</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5794,15 +5289,11 @@
           <t>1.负责公司业务在新媒体或社交媒体平台上的引流与推广（包括但不限于各个平台如微信群，qq群等私域公域的账号的运营推广、内容运营、粉丝引流等）； （大白话：工作内容主要上从各种途径将意向客户引导进我们的私域运营） 2.协助微博、微信、抖音、小红书等社交媒体的营销策划/推广/运营；需要对矩阵内容负责简单文案及资讯； （大白话：有的时候还需要帮忙写一些简单的宣传文案） 3.协助策划传播方案并组织相关推广活动或新媒体推广计划，提升用户活跃度，能够充分利用平台特性及优势，提升曝光度等，挖掘并分析目标群体，开拓新用户； （大白话：有的时候还需要出主意，看看有什么方法可以扩大曝光，获得更多精准客户） 4.对用户需求并且给予反馈收集及竞品公司运营情况进行 BP分析及总结，并提出合理优化建议； （大白话：看看同类型的业务公司最近有什么新动态或好的创意）</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>内容运营</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5835,15 +5326,11 @@
           <t xml:space="preserve">[6 months, 4-5 days/week] Name of Project: Autolabeling development and VLA POC project Objectives: - In this position, you will be part of the AD and AI algorithms team in R&amp;D China. You will work closely with AD research and engineering teams to design and develop advanced automated driving and parking functions specifically for Chinse customers. Your primary focus will be on perception and fusion function development to fulfill the system requirements under challenging highway, urban, and parking scenarios. Main Tasks: 1. Perception pipeline development - Support to develop ADAS perception </t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>C++、PyTorch、Python、TensorFlow、人工智能、多模态、大模型、机器学习、深度学习、计算机视觉</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5876,11 +5363,6 @@
           <t>我们是BA国际，一家起源于澳大利亚，专注于国内外硕博申请全流程服务、科研背景提升、AI教育平台、签证办理、留学课业辅导的一站式留学深造平台。核心团队均来自国内外顶尖高校及科研机构，凭借专业的教研实力、完善的服务体系和优质的口碑，已帮助数千名学员实现名校升学目标，解决留学全周期难题。现因业务高速扩张，诚邀优秀新媒体运营人才加入，共拓留学教育行业新蓝图！ 招聘岗位：新媒体运营 岗位职责 账号全周期运营：负责矩阵账号运营，包含小红书、微信公众号等核心社交媒体账号的内容策划、编辑、发布及维护，包括选题构思、文案撰写、图文/短视频制作、评论互动等，聚焦海外硕博申请、科研提升、签证办理、留学课业等核心业务，提升账号曝光量、粉丝量及活跃度。 客资拓展：基于账号内容及平台流量，通过私信回复、评论引导、社群运营等方式，挖掘潜在客户：有硕博申请、科研提升、签证办理、留学课业辅导需求的学生家长，完成客资数量指标，为销售团队输送高质量意向客户。 内容与销售联动：结合公司全流程服务（硕博申请规划、科研项目匹配、Al教育平台、签证代办、留学课业辅导等），策划兼具专业性与吸引力的内容话题（如申请避坑、签证材料清单、课业难点突破等），精准触达目标人群，强化用户需求感知，助力客资转化。 数据跟踪与优化：定期分析账号运营数据（阅读量、点赞）任职要求 专科及以上学历，市场营销、新媒体、广告学等相关专业优先，熟悉留学赛道</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5913,15 +5395,11 @@
           <t>职位描述1、负责部门数据统筹分析，及数据监控工作，协助完成部门汇报工作； 2、协助进行电商主播的运营工作，通过数据分析调研等手段，了解挖掘主播在平台的生存现状及机会点； 3、负责部门工作流程化梳理，形成SOP任职要求1、要有稳定性，至少实习三个月； 2、具备较强的数据分析能力，能够熟练使用办公软件； 3、积极主动，具备良好的协作沟通能力，有相关实习经验优先； 4、具备强烈的责任心与抗压能力，能够适应快节奏的工作环境，每周至少工作4天以上，可远程办公； 5、2026届应届毕业生优先，表现优异者有转正机会。</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5954,15 +5432,11 @@
           <t>工作职责： 1. 协助主数据清洗 2. 协助销售数据核实及整理 3. 协助部分系统的运营及管理 4. 部门其他支持工作 岗位要求 1. 每周出勤3-5天，至少实习6个月以上；优先大三或研一研二 2. 精通Excel等Office办公软件 3. 优秀的责任心及学习能力 4. 有长期在医药医疗行业发展的期望 公司：长春金赛，央企上市药企 地点：漕河泾，地铁9/12/15号线</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>Excel、办公软件</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5995,15 +5469,11 @@
           <t>【岗位职责】 1.负责数字化项目现场系统的日常巡检、故障排查与问题修复，保障系统稳定运行； 2.配合开发团队完成新线拓展； 3.参与数字化项目的前后端功能开发； 【岗位要求】 1.本科及以上学历，计算机应用与科学、软件工程、电子信息专业等相关专业； 2.掌握后端开发语言（java/Python），具有良好的编程基础与代码规范意识； 3.学习能力强，对数字化技术有浓厚兴趣，愿意主动钻研新技术与新业务场景； 4.具备良好的问题分析与解决能力，能快速定位并处理开发中的常见问题； 5.有数字化项目开发/运维实操经验的优先；</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>Java、Python、后端</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6046,9 +5516,6 @@
           <t>Agent、PPT、Word、人工智能、办公软件、物联网</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6081,11 +5548,6 @@
           <t>职责描述： 1、内容策划与创意发散：协助团队以营销目标为基础、对社交媒体（如抖音/红书/腾讯等）的广告传播内容与创意形式包装，推动不同营销节点的项目执行； 2、内容素材协助：敏锐捕捉社交媒体最新热点，参与广告视频脚本的初步构思、文案撰写；协助进行图片、视频等广告素材的灵感收集与提案，将想法转化为与品牌调性相符的创意内容； 3、竞品与案例研究：协助收集、整理各平台内容数据，跟踪分析同业优秀案例，吸收先进玩法，为团队带来新的灵感和思考。 任职要求： 1、学历专业：2026届或2027届毕业的在校生，市场营销、广告学、新闻传播、中文等相关专业优先； 2、核心能力 ：“有网感”深刻理解不同平台的调性和内容逻辑，知道什么样的内容能引发用户共鸣和互动。“懂内容” 具备良好的文字功底和审美能力，能够判断内容的好坏。“有想法”对视频脚本、文案、视觉设计有基本认知，具备良好的学习能力和主动性； 3、在岗时间：每周至少保证4天以上出勤，全勤实习期三个月以上优先。</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6118,15 +5580,11 @@
           <t>【岗位职责】 1、负责目标语种与中文的双向翻译工作，涵盖各个行业等多场景文本，确保译文准确、流畅，符合目标市场语言习惯与文化特点；​ 2、协助完成翻译内容的校对、质检与术语统一，维护语种专属术语库，保障翻译质量一致性；​ 3、参与 AI 翻译辅助项目，修正人工智能生成文本的语法、逻辑偏差，优化训练数据质量；​ 4、、配合团队完成多语种内容本地化适配（如日语敬语规范、西语拉美与西班牙用词差异调整），避免文化禁忌；​ 5、、协助整理翻译项目资料、跟进交付进度，完成领导交办的其他语言类辅助工作。 【任职要求​】 1. 核心语言能力​ -日语：JLPT N1 ，韩语：TOPIK 6级，德语：歌德C1 ，西班牙语：DELE C1 ，持有 CATTI 笔译证书者优先；​英语：专八 ，持有 CATTI 笔译证书者优先； -目标语种读写译能力扎实，能精准理解原文语境与专业术语，中文表达流畅规范，可独立完成双向互译；​ -了解对应语种国家 / 地区文化习俗、语言变体（如德语区方言、西语拉美变体），避免翻译中的文化冲突。​ 2. 技能与工具​ -熟练使用 Word、Excel、PPT 等办公软件，掌握 Word 格式排版、Excel 术语整理技巧；​ -熟悉至少 1 款 CAT 工具（Trados、MemoQ、SDLX 优先），或具备 Xbench、Aegisub 等辅助工具使用经验者加分；​ -可运</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>Excel、PPT、Word、人工智能、办公软件、大模型</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6169,9 +5627,6 @@
           <t>人工智能、大模型、数据分析</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6204,11 +5659,6 @@
           <t>岗位职责 1、达人挖掘与商务谈判：根据项目需求，在小红书、抖音等平台挖掘匹配的达人（KOL/KOC）。独立负责建联、价格谈判，在保证合作质量的前提下，争取最高的性价比和合作权益。 2、内容审核与协作：结合达人的账号风格和产品卖点，把控Brief方向，高质量完成达人脚本/笔记的审核，确保内容符合品牌要求。 3、数据追踪与复盘：对合作内容进行全流程的数据追踪，定期统计、分析推广数据（如曝光、互动、转化等），及时反馈异常并主动提出优化建议。 任职资格 1、熟悉小红书/抖音等内容渠道，了解平台的爆款逻辑，是社交媒体的重度用户。 2、有极强的责任心和执行力，能在规定时间内推进任务完成发布。 3、具备良好的商务沟通和谈判意识，懂得如何与达人沟通合作细节，控制合作成本。 4、对数据有一定敏感度，能熟练使用Excel进行基础的数据统计。 5、2027年及以后毕业，能稳定实习至少3个月的时间。 加分项： 1、网感好、有梗，对当下的网络热点和潮流风向把握准确。 2、有过往谈价成功的案例，或对渠道价格体系有一定了解。 3、能尽快到岗，实习时间稳定。 实习津贴： 150元/天+20元餐补/天</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6241,11 +5691,6 @@
           <t>职责描述： - 协助处理英语AI配音项目管理事宜； ﻿- 协助音频数据处理、发音评测、重音及韵律情感标注反馈； ﻿- 协助处理英语AI配音相关测评数据； - 协助进行配音台词比对/润稿工作。 任职要求： - 本科及以上学历的在校生； - 具备良好的英语听说读写能力，英语发音标准，能够准确理解和审核英文音频资料； - CET-6及以上同等英语水平、有配音相关经验优先； - 对待工作严谨认真，思维活跃，责任心强，能承受一定的工作压力。</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6288,9 +5733,6 @@
           <t>Django、Flask、MySQL、Python</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6333,9 +5775,6 @@
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6368,15 +5807,11 @@
           <t>【岗位背景】 【岗位描述】（你将做什么） 1. 运营协助 · 协助店长处理日常行政事务，如排班协调、考勤统计、库存盘点及报表整理。 · 监督店铺环境的整洁与陈列标准，确保货架丰满、卫生达标，营造舒适的购物环境。 2. 服务支持 . 收集顾客反馈，提升顾客满意度。 · 协助店长管理门店的客户社群（如微信群/企业微信），发布新品信息及护肤小贴士。 3. 货品与陈列管理 · 协助店长进行收货、验货及退换货处理，确保库存准确无误。 · 根据店长指导，调整和优化商品陈列（如换季陈列、节日主题陈列），提升产品吸引力。 4. 新媒体协助（加分项） · 协助进行简单的店内直播、产品短视频拍摄或小红书/朋友圈素材拍摄。 5. 电商运营经验（加分项） . 协助淘宝店运营 【任职要求】（我们希望你） 基本条件： · 在校大学生或应届毕业生，专业不限（市场营销、电子商务、美容化妆相关专业优先）。 专业技能与素养： 1. 热爱美妆，紧跟潮流：对彩妆、护肤品有浓厚兴趣和基本了解，是小红书、抖音、B站的美妆深度用户，熟悉主流品牌。 2. 形象气质佳：注重个人仪表，对美有追求，愿意展现精致的职业形象（可在入职后享受员工内购折扣进行自我提升）。 3. 沟通能力强：性格开朗，乐于与人沟通，具备亲和力和服务意识，没有玻璃心。 4. 学习能力强：愿意从基础做起，快速掌握产品知识、销售技巧及收银系统的使用。 5. 踏实细心</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>Excel、办公软件</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6419,9 +5854,6 @@
           <t>内容运营</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6464,9 +5896,6 @@
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6499,15 +5928,11 @@
           <t>1、参与亿级用户规模的视频推荐优化，提升停留时长、点击率、留存率等核心指标； 2、参与机器学习、深度学习领域的技术研发工作，包括但不限于深度模型设计与优化、强化学习、迁移学习、图神经网络等的算法和系统研发等； 3、分析海量用户行为数据和视频数据，增加有效的特征，挖掘用户兴趣，优化排序机制； 4、通过超大规模机器学习模型和系统，使用先进的检索和排序手段，优化社区生态，优化快手短视频推荐效果； 5、针对海量用户行为数据，提供分布式的算法实现的解决方案，大幅提升算法计算规模和性能； 6、参与搭建推荐系统框架，提供高并发，大数据，高效可靠的线上服务； 7、参与全域流量博弈的机制设计，协助拓展业务边界； 8、参与前沿问题探索与研究，结合实际应用场景，提供全面的技术解决方案。</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>大数据、强化学习、推荐系统、机器学习、深度学习</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6540,11 +5965,6 @@
           <t>主要工作： 1、协助开展公司合规体系和合规制度的建设； 2、协助开展法制宣传教育培训工作； 3、协助开展内部审计相关工作； 4、领导交办的其他工作。 要求： 1、本科以上学历，法律、经济、审计及相关专业，参加过专业相关考试者优先； 2、熟悉国有企业合规制度，了解国家合规管理相关知识； 3、具有较强的责任心，良好的沟通能力和团队协作精神，踏实勤奋，身体健康。</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6577,15 +5997,11 @@
           <t>岗位职责： 1.协助主管负责social plan的撰写和整理，包括但不限于：500强品牌分析、用户洞察、整合营销策略、媒体及综艺推荐、KOL把控等； 2.在各社交平台（抖音/快手/B站/小红书/微博/微信）搜索并推荐适合的KOL/KOC； 3.把控social media &amp; KOL 的产出内容，跟进执行包括但不限于跟进KOL脚本、把控视频拍摄等； 4.协助进行团队其他日常工作。 任职要求 1.本科或研究生在读，对社交媒体感兴趣； 2. 除考试等特殊情况外，希望一周到岗5天； 3. EXCEL技能务必熟练，逻辑和数字能力强 4. 有国内social公司/MCN经验，有达人经验的优先 5. 日常实习，需要四月初到岗，暑期实习勿投</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6618,15 +6034,11 @@
           <t>关于我们 我们正在打造一个以水晶为核心品类的全球化独立站电商品牌。 我们的目标是构建一个具备：清晰品牌叙事、国际市场定位、高端视觉表达、可持续商业模型的长期品牌资产。 我们正在寻找的角色是全球品牌构建核心成员。 你将深度参与品牌从 0 到 1 的构建全过程，包括：水晶产品设计与系列规划、品牌视觉与表达体系、独立站结构与增长优化、海外市场开发与资源拓展、内容输出与品牌叙事构建、行业资源整合与趋势判断。 我们希望你能够站在“品牌整体”的高度思考，而不是只完成某一个模块。 核心参与方向： 一、水晶产品设计与产品体系构建 参与水晶产品创意设计与结构规划 构建产品系列的统一风格与品牌识别度 结合市场趋势与文化表达进行创新 参与打样、优化与长期产品规划 我们重视产品的文化表达与长期价值，不仅是销售转化。 二、品牌视觉与品牌叙事 参与品牌定位与视觉方向制定 构建品牌故事与核心价值表达 将品牌理念转化为视觉与内容体系 统一官网、社媒与传播语言 三、独立站增长与SEO体系 参与独立站结构规划与优化 建立SEO基础逻辑与内容增长模型 优化产品页结构与转化路径 理解搜索、流量与品牌长期资产之间的关系 四、海外市场与国际化拓展 参与海外市场策略制定 建立国际资源网络 理解不同市场文化与消费心理 构建长期国际发展路径 五、行业交流与认知升级 品牌的成长离不开行业认知的持续升级。 我们鼓励核心成员： 主动参与</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6669,9 +6081,6 @@
           <t>Agent、Git、PyTorch、Python、TensorFlow、人工智能、多模态、大模型、强化学习、微调、机器学习、深度学习</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6704,15 +6113,11 @@
           <t>Note: Please attach bilingual resume with title: Name-School-Major-Grade. Location: Shenyang city in Liaoning province. On-Board month: April of 2026. Job Description: As part of BMW China R&amp;D division, you will support the development of innovative high-voltage battery systems within a cross-functional team. This role offers a unique opportunity to gain hands-on experience in cutting-edge automotive technology while contributing to project and team. Key Responsibilities: - Assist in the development of high-voltage battery systems in close collaboration with technical experts. - Coordinate wit</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>Excel、PPT、Word、办公软件</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6745,11 +6150,6 @@
           <t>职位描述： 1.重点负责网易上流的内容选题策划、编辑； 2.参与网易上流热点内容写作，转载文章排版优化，风格可参考往期内容； 3.负责工作室第三方平台新媒体内容运营（主微博、小蜜蜂） 职位要求： 1.熟悉网易上流以往栏目风格及文章调性，了解读者定位； 2.有新媒体实习经验（熟悉公众号后台），有写作经验，有个人作品，熟悉新媒体生态，对数据敏感； 3.善于追热点，逻辑清晰； 4.有较好的文字和图片审美，有良好的资料检索能力，对ai有一定的摸索和运用能力。 需要附上： 1.往期作品、案例链接（青年文化、地域文化领域优先考虑）； 2.根据公众号网易上流往期内容，策划三个选题，要求地域文化或青年文化方向，格式：标题+论点+简单大纲。</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6782,15 +6182,11 @@
           <t>【岗位职责】 1、协同梳理写字楼项目及产品特色及特点，制定并策划推广策略； 2、协同探索写字楼项目产品推广新模式研究； 3、负责写字楼产品空间规划、创新整合空间使用功能，并依据方案制作平面布局图、效果图等； 4、写字楼项目产品与推广视觉优化并输出方案。 【任职资格】 1、建筑学、室内设计、环境艺术设计、平面设计等相关专业背景优先，优秀者可放宽专业背景要求； 2、熟练运用建筑制图、3D建模、渲染软件及平面设计类软件，如CAD、3ds Max、SketchUp、渲云、AI、PS等软件； 3、有美术基础，具备材料、工艺理论基础知识，有良好的审美能力； 4、对策划推广工作具备一定的热情和兴趣； 5、能够快速适应工作，细心负责，工作态度踏实认真，有较强的沟通表达能力。</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6833,9 +6229,6 @@
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6868,11 +6261,6 @@
           <t>岗位职责： - 社交媒体撰写以及排版 - 传统媒体关系维护 - 翻译 - 活动支持 岗位要求： - 英语良好，工作中需要用到英语，包括文档翻译和资料收集等 - 熟悉微信排版 - 有基础图片及视频编辑能力 - 一周至少保证3天出勤，希望是能实习三个月或者以上 - 专业不限，请投递中英文简历</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6915,9 +6303,6 @@
           <t>SPSS、SQL、Tableau、大数据</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6950,15 +6335,11 @@
           <t>Department Mission The R&amp;D project team is seeking an intern to assist with daily tasks on R&amp;D and CEA projects.Support daily document organization, as well as basic coordination and communication tasks.Partially or indirectly involved in Android App-related development work. Your Responsibilities Assist the R&amp;D project team in daily task support for R&amp;D and CEA projects to ensure efficient project progress. Be responsible for daily documentation organization, data compilation, as well as simple cross-departmental coordination and communication work. Be responsible for daily documentation orga</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>Android、Excel、PPT、Python、办公软件</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6991,11 +6372,6 @@
           <t>1、负责产品的商业化运营相关工作，参与产品优化、制定产品运营方案，包括但不限于制定产品推广策略、运营激励策略、案例和方法论挖掘等，同时定期收集反馈，优化提升产品使用率及收入； 2、深入了解业务，以提升业务体验和效率为目标，发现业务流程和产品中的优化点，通过产品化工具化形式对平台功能进行优化迭代，做到最大化业务赋能； 3、参与研究分析当地商业化相关趋势，为内部和客户提供相应信息支撑。</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7038,9 +6414,6 @@
           <t>Excel、PPT、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7083,9 +6456,6 @@
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7128,9 +6498,6 @@
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7173,9 +6540,6 @@
           <t>Excel、SQL、人工智能、数据分析、机器学习</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7208,11 +6572,6 @@
           <t>岗位职责： 1.负责基础和业务的架构设计和研发工作，解决各类有技术挑战的问题，为产品和业务的发展提供最强有力的技术支撑 2.按照软件开发流程，根据产品和项目计划，完成所负责模块的架构设计、编码、测试和文档编写的全流程工作 3.持续优化系统架构，提高系统在高并发、高流量和分布式环境下的容灾容错能力，保证系统的高可用性、高可靠性和高扩展性 4.承担新技术预研和方案选型，参与关键技术点的攻坚工作，帮助团队内的技术推广。 任职要求： 1.2027属届毕业生，本科及以上学历，喜爱计算机以及互联网技术 2.扎实的数据结构和算法能力，熟悉常用的数据库技术 3.精通至少一种开发语言，并能熟练应用解决具体问题； 4.有较强的学习能力，有强烈的责任心和自我驱动力; 5.能及时关注并学习业界最新技术，具备良好的沟通能力和团队合作精神。</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7245,11 +6604,6 @@
           <t>知乎会员业务经营分析 职位描述： 1、与产品、运营、增长、内容等团队配合，参与知乎会员及漫剧业务的研究与经营分析工作 2、结合业务实际表现、用户认知及行业洞察，协助制定业务目标，发现机会点及可下钻问题 3、支持周报、数据分析、专家访谈、用户研究等日常工作 职位要求： 1、有内容行业实习经历、对小说、泛娱乐行业有热情加分 2、能够实习3个月，表现良好有转正机会 3、学习能力强，工作热情高，逻辑及表达能力在线</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7282,11 +6636,6 @@
           <t>招聘职位：Taskforce Consultancy新媒体实习生 到岗时间要求：实习时间不少于三个月，每周到岗时间不少于四天 - 配合客户主任，针对客户的新媒体传播需求进行创意策划； - 参与客户传播方案的落地执行； - 基础调研及内容撰写； - 学习基础的新闻及公关写作，并尝试独立完成任务； - 执行客户经理安排的其他工作，如新闻信更新； 任职要求 - 大三以上本科生或研究生在读，专业不限，新闻、广告、公关、市场营销、外语类、法律、行政管理等专业优先； - 熟悉互联网及平面媒体、电视媒体的运作规律； - 对公关业内信息有一定的敏感度； - 有优秀的中文书面和口头能力，英文书面与口语能力佳者优先考虑； - 善于学习、热爱新鲜事物； 关于 Taskforce Taskforce Consultancy (上海思达托赋管理咨询有限公司) 是一家专业的战略咨询、公共关系与品牌营销公司。 我们基于战略梳理与品牌定位，开展核心利益相关者管理以及品牌公关传播活动，在快速变化的经济社会发展进程中、纷繁复杂的媒介及中外舆情环境中，为企业发展赋能，扩大组织声量，实现企业和组织的快速成长、品牌的迅速增值和全球化发展。</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7319,15 +6668,11 @@
           <t>Main Purpose of the Job: Assist in cleaning and analyzing sales data, building automated dashboards, and participating in sales forecast modeling. Improve sales forecast accuracy, enhance marketing investment ROI, and optimize supply chain &amp; resource allocation efficiency. Main Responsibilities： 1) Consolidated and stored diverse business-related data to support company operations 2) Leveraged statistical methods, data mining, and machine learning to generate actionable business insights 3) Visualized analysis results and delivered reports via Excel, Power BI, and other tools 4) Data Productiz</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>Excel、Power BI、数据挖掘、机器学习</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7360,11 +6705,6 @@
           <t>职责描述： 工作职责： 1. 支持部门级整体工作 2. 两轮车公开渠道市场调研和材料更新 3. 项目管理助理，任务跟进和会议纪要整理 4. 支持研发岗位具体文档工作及测试工作 5. 其他行政工作 任职要求： 任职要求 1. 实习职时间至少3-6个月，每周5天全勤优先考虑 2. 辅助智能驾驶相关专业优先（电子/自动化/车辆工程/软件等专业） 3. 性格活泼，人际交往能力强 4. 热爱摩托车，电动车，有驾照优先 5. 英语/日语/德语优先 6. 喜欢新事物/黑科技同时也能耐得寂寞、踏实工作</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7407,9 +6747,6 @@
           <t>内容运营</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7442,11 +6779,6 @@
           <t>工作内容 : 公司内部资料整理、归档 公司内部招聘事务 公司流程梳理 报告撰写等事务。 任职资格： 本科或以上学历，实习生可转正 踏实，肯干，条理好，学习能力强</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7489,9 +6821,6 @@
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7524,15 +6853,11 @@
           <t>岗位职责 1、深入理解国际化外卖业务，参与国际化外卖用户交易履约体验优化的日常产品工作。 2、收集并发现用户在使用中的体验问题，基于用户视角出发提出合理的解决方案。 3、协助竞品调研，掌握行业发展趋势，根据行业变化迭代产品。 4、组织协调与设计、研发相关的各种资源，保证项目的顺利运转及按时交付。 任职资格 1、本科及以上在校生，有【葡语】和英语能力，具有一线互联网产品工作实习经历优先 2、有同理心，对产品有好奇心及探索意愿 3、逻辑严谨、沟通能力强，有一定的sql数据分析能力优先 4、可连续实习3个月及以上，每周可到岗4天及以上</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>SQL、数据分析</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7565,15 +6890,11 @@
           <t>工作内容 1、可独立承接资源及投放管理 2、协助数据整理并输出效果反馈、制作报告等; 3、协助进行电影日常项目及产品的运营工作 4、协助完成部门其他日常运营事务; 职位要求 1、在校生、统计学、计算机、数学等相关专业优先; 2、熟练使用 Excel透视分析、VLOOKUP等基础数据工具及office 办公软件: 3、学习能力强、细心认真、有责任心、有数据分析相关经验优先 4、热爱电影,了解新媒体尤其微博 5、每周出勤4-5天,需线下坐班,实习期 5个月以上。 你能得到 *国内重要娱乐宣发平台/互联网上市公司实习经验 *了解行业的基本运作 *实习津贴及证明</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
           <t>Excel、办公软件、数据分析</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7616,9 +6937,6 @@
           <t>C++、Java、Python、人工智能</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7651,11 +6969,6 @@
           <t>职位描述: 日常实习：面向全体在校生，为符合岗位要求的同学提供为期3个月及以上的项目实践机会。 团队介绍：抖音是一个帮助用户表达自我，记录美好生活的短视频平台。截至2021年6月，抖音日活跃用户超过6亿，并继续保持高速增长。加入我们，你将为亿万用户创造更好的产品，让用户看见更多样的世界。 1、负责平台热门/潜力游戏洞察，熟悉各类型游戏品类玩法，有游戏理解深度和广度，可以敏锐捕捉游戏趋势发现潜力游戏，总结梳理相关特点规律； 2、负责游戏品类玩法运营，熟悉抖音生态，挖掘抖音结合小游戏的产品功能结合点，分析现有产品数据，包括产品功能和游戏付费设计、玩法设计等，输出产品平台运营优化方案； 3、基于游戏活跃和流水等经营目标，输出节点运营方案、抖音生态内的游戏内容洞察，指引服务游戏开发者做平台经营。 职位要求: 1、本科及以上学历在读； 2、每周4天及以上工作时间，实习3个月以上； 3、熟悉小游戏各品类/玩法特点，游戏经验丰富，熟悉游戏运营过程，理解用户留存、付费等逻辑； 4、熟悉游戏内容生态（包含视频、直播、图文），了解游戏达人、机构等，对游戏内容与游戏产品结合理解； 5、有游戏策划/发行实习经验优先； 6、具备良好沟通能力、统筹协调能力，自驱力强，有强烈的责任心并热爱游戏。</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7688,15 +7001,11 @@
           <t>1、参与快手容器云资源调度及服务编排等领域的设计与开发工作； 2、基于Kubernetes等云原生技术完善资源统一调度、服务的多集群联邦编排，提升资源及服务变更效率； 3、参与公司在离线混部系列机制的设计与开发，提升集群异构资源的使用效率； 4、探索容器领域前沿技术，参与容器云全局技术优化与落地实践。</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>Kubernetes、云计算</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7739,9 +7048,6 @@
           <t>人工智能、办公软件</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7774,11 +7080,6 @@
           <t>岗位职责： 1，拍摄剪辑：负责拍摄剪辑策划短视频或综艺等相关名人明星节目，需要拥有专业的拍摄和剪辑技能，有优秀作品者优先 2，其他执行配合：协助支持部分名人明星账号日常对接维护，活动项目执行等事宜 ?任职基本要求： 1，本科以及以上学历，专业不限，有文案功底以及视频拍摄剪辑经验优先（需要自带摄影装备） 2，热爱新媒体行业，具备优秀的沟通能力，能够与不同背景的名人明星嘉宾建立并维持良好的互动关系 3，责任心爆棚：对待工作认真负责，注重细节，能够独立完成任务并追求卓越。 4，团队精神：具备团队合作精神，能够与团队成员紧密协作，共同在短视频直播赛道上创造佳绩。 5，每周到岗5天，实习6个月以上，能够长期实习者优先 ?加入我们，你将获得： 与名人明星以及短视频直播领域的佼佼者亲密接触的机会，拓宽你的人脉圈。 来自实战经验丰富的导师指导，助你在短视频直播赛道上快速成长。 ?快来加入我们吧！搜狐视频关注流期待你的加入，一起在短视频直播赛道上创造更多精彩瞬间！</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7811,15 +7112,11 @@
           <t>一、企业简介 前海仁智资本管理（深圳）有限公司成立于2015年，是一家专注早期硬科技的风险投资机构，在管基金获得了深圳市、区两级财政出资。2025年，仁智资本成功入选了全国信息技术标准化技术委员会成员单位、工信部人工智能标准化技术委员会成员单位。仁智资本也是北京丘成桐科学基金会和清华大学教育基金会的捐赠机构。 二、职位发展规划 选拔具有专业素质、商业意识、发展潜力的优秀人才作为仁智新生力量，使新生力量在短期内快速了解整个公司体系运作机理，包括项目挖掘、投资运营、投后管理等业务，以培养与公司价值观、理念一致的优秀人才，与公司共同发展。 三、工作职责 1.负责发掘优质初创公司 2.负责维护科技人才资源 3.负责跟进已投项目 四、任职要求 1.金融、经济、投资、市场营销、人文社会科学、新闻传播、音乐等相关专业以及数据科学、计算机、数学等相关专业优先； 2.对投资、科技领域充满热情，性格开朗，具有良好的沟通能力、良好的团队合作精神，有责任感和较强的学习能力； 3.具有清晰的逻辑思维能力以及良好的解决问题能力。 五、福利待遇 1.基本工资5k起/月+绩效奖金； 2.与优秀CEO、行业专家、科学家近距离学习的机会； 3.与优秀的博士团队一起工作。</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>人工智能、数据科学</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7852,15 +7149,11 @@
           <t>1. 参与业务需求分析与设计，参与开发侧软件架构设计及相关实现方案等 2. 参与软件架构设计、开发平台管理，参与软件组件架构定义及核心组件开发及优化； 3. 参与制订代码规范、接口规范等开发模板，参与新技术调研与引进； 4. 负责软件代码开发、调试与维护；</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>产品设计</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7903,9 +7196,6 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7938,15 +7228,11 @@
           <t>1、产品安全测试，安全评估，以及代码安全审计； 2、对网络入侵，业务风险事件进行响应处理； 3、跟踪安全动态，研究前沿安全技术，对互联网重大安全漏洞进行响应分析； 4、快手安全相关系统如企业安全网关、扫描器、WAF、4A系统、入侵检测、漏洞挖掘、安全大数据分析平台开发、建设。</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>大数据、安全测试、漏洞分析</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7979,11 +7265,6 @@
           <t>1、根据游戏整体的设计框架，完成游戏内关卡或活动的设计和制作； 2、根据游戏的世界观设定和区域规划，负责设计和制作。</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8016,11 +7297,6 @@
           <t>主要职责： 1. 实习期间，将作为咨询业务线在深圳办公室的联络人，支持业务所需的各类事务性工作和跨部门的协作（包括与财务部，人事部等相关人员的沟通和协调） 2. 协助销售阶段所需的材料整理和归档，并帮助团队完成销售阶段的内部流程，包括合同打印，盖章，送递等； 3. 协助项目数据后期的整理，分析和归档； 4. 支持实习生招聘工作，包括简历初筛、简单电话联系、笔试/面试邀请，并协助完成公司内部人事线上/线下的档案管理流程（入职、离职、续聘等相关工作） 5. 其他临时事务性工作 时间：确保办公室on-site 支持不少于3天/周，远程1天，每周4天-5天工作时间；时间要3个月及以上； 目前人就在本地，能尽快上岗的优先。 办公室地址：深圳市福田区中心四路一号嘉里建设广场T-1座8楼801-802单元</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8053,15 +7329,11 @@
           <t xml:space="preserve">项目描述： 【滚石计划】暑期训练营是顽岩资产为全球Top学子打造的专属实习项目，致力于培养下一代量化策略研究员（QR）与量化开发工程师（QD）。在为期两个月的训练营中，你将直面业务真实场景，参与探索公司前沿项目，用实战快速提升研究和工程能力。 主要职责： 1. 深度参与多个核心技术平台的开发及维护，根据专业方向及团队需求，参与到不同领域的重点项目之中； 2. 为策略研究和交易提供框架开发支持，协助策略实现和交易执行； 3. 根据用户需求，设计AI驱动的解决方案和工具提高研究和决策效率； 4. 方向包括但不限于：C++ 交易系统开发、python量化开发、AI Infra开发等。 我们正在寻找这样的你： 1. 2027届及之后本、硕、博毕业生； 2. 计算机、软件工程、人工智能、金融工程等理工科相关专业； 3. 具备扎实的编程能力，精通 C++、Python 或Golang等任意一个编程语言； 4. 具备强烈的学习动力、解决问题的能力和良好的团队协作精神； 5. 无需金融背景，但对量化金融领域有浓厚兴趣，渴望深入技术实践。 我们提供： 1. 现场接触真实研发环境，使你专注于纯粹的技术发展； 2. 获得一线资深技术专家的亲身现场指导，快速积累实战经验； 3. 根据你的开发经历和兴趣方向，制定专属的职业发展路径，助你独立推进各个方向的设计开发和研究，进一步探索新的工程和技术极限； 4. </t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>C++、Go、Python、人工智能</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8104,9 +7376,6 @@
           <t>Excel、PPT、大数据</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8139,11 +7408,6 @@
           <t>岗位职责： 1. 负责公司日常服装快递拆包盘点，跟进订单进度； 1. 管理日常仓储作业：拆包质检、拣货、打包发货及退换货处理； 2. 做好系统内各物流与订单匹配规则的运维，优化清关申报等事项； 3. 持续优化工作流程，提升工作效率，确保订单准确及时发货； 任职要求： 1. 有一定的英语基础能力； 2. 熟练使用ERP系统进行订单、库存、采购数据管理； 3. 了解女装类目质检标准（如线头、污渍、吊牌、做工等）； 4. 具备学习能力，熟悉采购发货流程，良好的沟通表达能力及团队协作精神（供应商、跨部门）； 5. 工作认真严谨有耐心，责任心强，有灵活解决问题能力，配合完成当日任务，主动维护仓库整洁 福利待遇： 1. 保障关怀：五险、定期零食下午茶和团队聚餐 3. 成长体系：专人一对一带教直至熟练上手 3. 晋升通道：可培养为供应链组长/主管 4. 工作氛围：扁平化管理，团队年轻有活力，拒绝内耗，专注成长与结果</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8176,15 +7440,11 @@
           <t>【岗位定位】 你将加入 Table for Six｜T46 增长团队，成为连接 内容产出 → 达人传播 → 流量增长。 你的核心任务，是让T46的优质内容和社交活动 被更多年轻人看到、喜欢、报名、转化。 具体来说，你要做两件事： 1.负责 达人（素人/ KOC / KOL）投放PR与日常运营； 你的目标，是让内容触达更广、转化更高、效率更稳。 【公司简介】 Table for Six (T46) 是一家把 夜生活、社交和 AI 重新组合的初创公司。 我们相信社交不该是尴尬的 networking，而是低负担的惊喜和化学反应。 在上海推出 盲盒酒局 Table for Six，T46：通过 AI 匹配 + 定制化社交剧本，让 6 个陌生人在周三晚上坐在同一桌，以最轻松的方式认识彼此。 现在，我们正在寻找一位 产品增长运营负责人，你将加入 Table for Six｜T46 增长团队，成为连接 内容产出 → 达人传播 → 流量增长 的关键中枢。 你的核心任务，是让T46的优质内容和社交活动 被更多年轻人看到、喜欢、报名、转化。 【岗位职责】 一、达人矩阵（KOC / 素人 / KOL）管理与扩招 【招募与搭建体系】 负责达人/KOC/素人招募，能通过多渠道扩招：小红书、微信群、兼职群、豆瓣、飞书、BOSS对接等； 设计分层结构（头部KOL / 稳定KOC / 活跃素人），并明确各层合作</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>人工智能、数据分析、项目管理</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8217,11 +7477,6 @@
           <t>【职位详情】 时间地点不限！不坐班，线上工作！！！非线下，按单结算 【工作内容】 1、不用自己写！有网感即可！根据公司提供的图文，进行内容的小红书&amp;抖音等相关的内容种草、笔记代发。 2、能及时沟通，关注自己的平台账号实时动向。确保账号权重优质，会有工作人员带教！ 【岗位要求】 1、有小红书&amp;抖音实名账号优先 2、小红书、抖音等新媒体平台重度用户，了解平台的流量机制。</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8254,11 +7509,6 @@
           <t>1、零件设计与制图； 2、研究性试验跟踪； 3、客户项目样件质量问题分析； 4、客户项目时间与TA计划跟踪； 5、样件生产技术问题跟踪与分析。 基本要求： 1、硕士研究生在读； 2、电气工程,机械电子,材料加工,高分子材料等相关专业； 3、英语良好； 4、每周3天以上，能稳定持续6个月。 飞书效率先锋认证优先</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8291,15 +7541,11 @@
           <t>——工作内容—— 1. 负责公司信息安全产品项目的售前售后技术支持工作； 2. 协助销售进行售前技术咨询、方案设计、产品测试、投标技术文档制作、讲标技术应答等工作； 3. 负责信息安全技术类文档的撰写，如：技术分析、竞争对手比较、培训ppt等; 4. 负责客户的的技术支持和产品培训工作。 ——能力与素质要求—— 1. 了解信息安全或网络产品工作； 2. 熟悉业界主流的安全产品,如防火墙、IDS、防病毒，漏洞评估工具等； 3. 具有积极主动的意识，能够独立解决问题及分析问题的能力； 4. 责任心强。具有良好的吃苦耐劳精神和团队合作意识； 5. 良好的文档能力，能够撰写技术文档； 6. 具有网络规划，产品测试及大项目实施经验； 7. 具有有技术支持及产品管理工作经验者优先； 8. 通过CCNP、RHCE、CISP、CISSP、ITIL、CISA等系统或信息安全相关证书者优先。 经验丰富者，薪资另议。</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>PPT、信息安全</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8332,11 +7578,6 @@
           <t>【职位详情】 时间地点不限！不坐班，线上工作！！！非线下，可提供实习证明 【工作内容】 1、不用自己写！有网感即可！根据公司提供的图文，进行内容的小红书&amp;抖音等相关的内容种草、笔记代发。 2、能及时沟通，关注自己的平台账号实时动向。确保账号权重优质，会有工作人员带教！ 【岗位要求】 1、有小红书&amp;抖音实名账号优先 2、小红书、抖音等新媒体平台重度用户，了解平台的流量机制。</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8379,9 +7620,6 @@
           <t>C++、Go、JavaScript、Linux、Python</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8424,9 +7662,6 @@
           <t>Docker、PyTorch、Python</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8459,15 +7694,11 @@
           <t>【岗位职责】 1、行业能力调研：研究多行业头部产品的 AI 导购能力，拆解交互特征，评估内容质量 2、AI 导购策略探索：结合电商场景需求，协助输出导购策略，探索“专业、有用、有趣”的 AI 导购交互 3、模型优化与效果评估：参与制定模型效果评估方案，推动模型输出质量提升 4、产品数据分析与复盘：参与产品上线前后的数据分析和效果复盘，通过数据梳理与思考，从数据中发现问题和机会； 【岗位要求】 1、关注潮流、电商相关行业趋势，具有产品相关实习or Al项目经验优先 2、对用户有深刻洞察，能站在用户角度思考，有个人爱好和产品体验追求者优先 3、一周在岗5天，实习期不少于3个月，能稳定实习者优先 4、学习能力强，敢于创新，脑洞大，具有强烈好奇心和自驱精神</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>人工智能、数据分析</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8510,9 +7741,6 @@
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8555,9 +7783,6 @@
           <t>办公软件</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8590,11 +7815,6 @@
           <t>日本市场头部的语音转写类效率工具产品 Notta正在寻找并肩奋斗的小伙伴。在这个职位，你会与用户充分沟通、互动，在产品与用户之间搭建桥梁。 ## 工作内容 1. 通过 Zendesk 系统及时解决客户的疑问。处理常见的客户咨询与工单，如退款申请、操作疑问等。 2. 工单分类。识别并按类型进行工单分流，例如合作或市场相关邮件转给市场、技术或产品问题转给开发/产品等，确保高效处理咨询来信。 3. 协助基础数据的统计、整理或其他支持性工作，支持团队高效运作。 ## 岗位要求 1. 日语流利（N2/N1），具备良好的书面与口头沟通能力。 2. 细心、责任心强，能够处理重复性任务并保持高准确率。 3. 对 SaaS 产品或客户服务有兴趣者优先。 4. 每周工作至少 20 小时。</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8637,9 +7857,6 @@
           <t>C++、NLP、PyTorch、Python、TensorFlow、机器学习、深度学习</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8672,15 +7889,11 @@
           <t>职位描述 1、协助建设全站的基础数据能力，提供丰富、稳定的短视频社区公共基础数据，探索更多数据能力的增量价值； 2、各类数据专题体系（如国际化业务）的建设，通过数据+算法+产品，赋能业务，提供全链路、可分析、可复用的数据能力，提供更直观、更具分析指导性的产品化能力； 3、建设公司层面的核心数据资产，与业务场景深度结合，为社区服务提供数据服务化、数据业务化的数据&amp;产品解决方案。 任职要求 1、24届及以后毕业的本科或研究生，能够连续实习3个月及以上，每周能保证全勤者优先； 2、计算机相关专业，有一定Java代码功底； 3、熟悉Hadoop数据体系，擅长实时或离线计算的实施优化； 4、有数据仓库或者PB级数据处理经验的优先。</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>Hadoop、Java</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8723,9 +7936,6 @@
           <t>CSS、Excel、HTML、Java、JavaScript、MongoDB、MySQL、Node.js、Power BI、Python、RESTful API、React、SQL、Vue、人工智能、前端、后端、大模型、数据分析</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8758,15 +7968,11 @@
           <t>【该实习岗位有转正机会，2027届毕业生优先，本科/硕士/博士均可】 **职位描述** 1、参与AI广告平台搭建，包括广告投放和创意智能生成等功能； 2、参与接入广告媒体平台API，将广告投放场景进行系统化抽象，构建可扩展的底层架构； 3、持续优化广告投放和业务增长策略，提升系统的自动化和智能化水平，打造高效的投放引擎； 4、了解技术前沿，运用AI技术持续优化系统架构。 **职位要求** 1、具备初步的系统架构设计能力，能进行系统抽象。有系统架构的实施和演进经验为佳； 2、扎实的编程基础，熟练掌握数据结构和算法，熟悉Python、GoLang、C++ 或 Rust 等至少一门编程语言； 3、熟悉并了解后端主流中间件的原理，如 PostgreSQL、Clickhouse、ELK 等； 4、额外加分项：有搜广推系统开发或用户增长平台研发经验者</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>C++、ClickHouse、Go、PostgreSQL、Python、Rust、人工智能、后端、用户研究</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8809,9 +8015,6 @@
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8844,11 +8047,6 @@
           <t>1、重点大学硕士以上学历，神经外科系或神经外科专业； 2、有三甲医院的工作经历优先，有杂志社编委工作经验者优先； 3、曾经发表多篇核心或者北大核心文章；擅于设计编辑神经外科专业稿件； 4、能够熟练处置神经外科常见急症及疑难病，擅长颅脑及脊髓损伤、颅内肿瘤、椎管内肿瘤、脑和脊髓血管性疾病、颈（腰）退行性疾病、脑外伤、脑和脊髓先天性疾病、中枢神经系统感染和寄生虫疾病、癫痫和帕金森等； 5、对待工作认真负责，态度端正踏实，能够高质量，高效率完 成稿件； 6、具有良好的职业道德素养，严格保密客户隐私； 7、热爱本职工作对编辑工作有较高的热情，有开拓创新精神； 8、欢迎应届毕业生，博士生优先 薪资待遇：年薪 20 万元以上 可在家办公，欢迎您前来合作！待遇优厚哦~</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8881,15 +8079,11 @@
           <t>职位描述 1、负责快手电商各产品的测试和质量保证工作； 2、根据产品设计或需求，进行需求分析，制定测试计划、风险评估、设计测试数据和测试用例，执行测试用例，准确定位并追踪问题等； 3、对线上问题进行持续追踪，并从中得出一些优化监控、测试方案提升等改进措施； 4、参与ui自动化、接口自动化、流量回放、故障演练、效能开发、AI建设等专项 任职要求 1、研究生学历，计算机/软件工程等相关专业，211/985优先； 2、有扎实的计算机基础，熟悉软件测试理论和方法； 3、优秀的代码基础，至少熟悉Java/Python/Ruby/JavaScript等主流语言中的一种； 4、具有良好的沟通能力和团队合作精神、快速的学习能力，思维敏捷、逻辑清晰、执行力强、工作责任心强、抗压能力强； 5、有互联网公司相关实习经验者优先； 6、实习至少6个月，能长期实习者优先，有AI经验者优先，实习期满后有转正机会。</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>Java、JavaScript、Python、产品设计、人工智能、单元测试、自动化测试</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8932,9 +8126,6 @@
           <t>C++、Python</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8967,11 +8158,6 @@
           <t>岗位职责： 1. 海外社交视频产品的投放，包括但不限于Facebook、Adword、Tiktok、unity等广告投放优化，管理多个广告账户 2. 不断挖掘海外适合产品的优秀的投放素材 3. 按照产品的目标要求，完成消耗的目标 岗位要求： 1. 本科学历，应届毕业生，或工作年限低于1年且有强烈意愿转岗者，英语能力较强者加分 2. 较强的学习能力和学习意愿 3. 逻辑思维能力强，对数据敏感，对素材理解能力强 4. 工作认真负责，强结果导向，表达能力强者加分</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9004,11 +8190,6 @@
           <t>此岗为短期实习岗，请认真投递 负责社区日常行政工作的流转顺畅。 协助餐厅维护、物资盘点、固定资产管理。 完成领导交办的其他行政事务。</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9041,11 +8222,6 @@
           <t>陪伴师侧运营支持 线上方向： 负责日常陪伴师注册咨询、答疑及引导，协助优化陪伴师入驻体验。 参与陪伴师社交媒体渠道的内容发布、素材收集与推广（如小红书、抖音）。 进行陪伴师侧流量、注册转化及运营指标的数据记录与分析。 针对陪伴师反馈与常见问题，协助完善 SOP、FAQ 与相关运营流程。 线下方向： 在老员工带领下参与高校、社区、兴趣社群等渠道的线下拓展活动，拓展优质陪伴师资源。 协助团队进行校园宣讲、线下活动组织、报名引导等基础执行。 针对潜在陪伴师群体（如大学生、自由职业者、兼职服务人员）进行初步介绍与信息采集。 协助形成线下拓展相关的总结、复盘与渠道名录。 岗位要求 学习能力强，愿意积极尝试新事物，能快速理解平台业务。 沟通能力好、亲和力强，愿意接触陌生人群体，敢于进行线下交流。 认真负责、有耐心、有同理心，理解陪伴师行业的特殊性和服务意义。 抗压能力一定程度可接受，能适应间歇性的高峰任务节奏。 具备校园社团、人际推广经验者优先；有线下活动组织经验加分。 每周可提供至少4天的工作时间。 你将获得 接触创新的陪伴经济与情绪支持行业的一线经验； 大厂背景团队的手把手指导； 参与从 0 到 1 的产品建设与运营机会； 线下拓展与用户运营能力的全面提升； 表现优秀者可获得长期合作机会或转正优先权。 工作方式 线上+线下办公</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9088,9 +8264,6 @@
           <t>PyTorch、计算机视觉</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9123,11 +8296,6 @@
           <t>职位描述: ByteIntern：面向2027届毕业生（2026年9月-2027年8月期间毕业），为符合岗位要求的同学提供转正机会。 团队介绍：抖音电商致力于成为用户发现丰富好物的首选平台。众多抖音创作者通过短视频、直播、商城等丰富的形式，给用户提供更个性化、更生动、更高效的消费体验。同时，抖音电商积极引入优质合作伙伴，为商家变现提供多元的选择。 1、参与平台商品质检体系的搭建与策略运营，参与制定抽检策略、质检任务追踪、供应商招采与管理等核心质检策略的制定与运营过程； 2、不断提升、完善平台的商品质检能力； 3、理解并通过数据指标变化发现业务问题，并推动解决方案落地。 职位要求: 1、2027届本科及以上学历在读，理工科背景优先； 2、对数字敏感，逻辑性好，愿意主动思考、理解业务； 3、工作积极、主动，可实习6个月以上。</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9160,15 +8328,11 @@
           <t>工作职责 1、参与人力资源管理咨询项目，协助顾问进行项目实施； 2、信息资料整理、PPT制作、数据分析等工作 ； 3、项目推进中其它工作； 任职资格 1、26应届，本科及以上学历，心理学、人力资源等相关专业优先； 2、严谨细致，认真负责，学习能力强沟通能力强； 3、涉及数据分析工作，Excel以及PPT的使用良好； 4、每周固定3天及以上的出勤时间，实习一个月左右的时间安排答辩，会有一对一带教； 5、实习薪资为180-200/天+300/月餐补，地点徐汇苑大厦； 流程为一轮测评+初试+复试，每轮节点会在1-2个工作日内给出结果</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>Excel、PPT、数据分析</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9201,11 +8365,6 @@
           <t>内容发布（可在家办公） 工作内容: 1、知识内容行业推广，内容已经制作好你只需要发布，无需自己产出内容。 2、薪酬结构： 内容发布薪酬：3元/单（含发10条任务，只发布 无需制作）； 3、可在家或者学校工作，也可以来公司上班，可开实习证明； 4、公司直招无任何费用，可长期实习！ 5、适合考公考研，但是需要实习证明，但是时间不充裕的同学。 工作时间: 不限 工作地点: 可在家或者学校，也可以来公司 内容轻松，适合考公考研没有额外时间到岗实习的同学</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9238,15 +8397,11 @@
           <t>【岗位：微博-党委 运营实习生】 ❣职位职责： 1.负责协助党委相关工作跟进、资料整理、项目支持； 2.参与线上活动策划与运营，线下活动筹备与执行； 3.协助进行党委相关稿件撰写、PPT、海报制作； ❣任职要求： 1.本科or研究生在读，熟悉微博产品，有自己的见解与思考，专业与新闻传播、文化艺术等相关者加分； 2.工作积极主动执行力强，学习能力强，具有良好的沟通能力和较好的学习能力 3.熟悉音视频软件，有良好的文字功底和数据分析总结能力，PS高手加分； 4.了解活动流程，有线上线下活动策划执行经验者加分； 5.一周出勤至少4个工作日，连续实习三个月以上； ❣你将获得： 弹性工作时间，舒适的工作环境，愉悦的工作氛围，不定期线下活动玩耍机会❤</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>PPT、数据分析</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9289,9 +8444,6 @@
           <t>AIGC、NLP、大模型、推荐系统、数据挖掘、机器学习、计算机视觉</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9324,11 +8476,6 @@
           <t>职位描述 1. CBU工具链宣传策划，平面设计，内容制作和推广活动(CBU-Cell Business Unit) 2. CBU文化和数字化体系落地宣传 3. 工具培训和运营 4. 协同专家制作培训教材，视频 5. 培训资料的编辑和管理 6. 培训和其它赋能项目运营 职位要求 1. 理工科或艺术类 2. 本科以上 3. 有运营经验 4. 擅长平面设计和美学基础 5. 性格外向，主动沟通 6. 逻辑思维能力 7. 新事物接受能力强 8. 视频制作能力 9. 有策划和文案能力，包括美工技巧和平面设计 10. 可以主持数字化活动 11. 可实习5个月及以上</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9361,15 +8508,11 @@
           <t>施展才华： 1、关注行业动态，保持市场敏锐度，了解同行业其他产品动向，输出市场及行业产品分析报告； 2、研究用户使用情况及效果，产出标杆案例及方法论； 3、通过数据分析、竞品分析、用户调研等方式，发现潜在需求和优化点，并协同落地； 有趣如你： 1、统招本科及以上学生，每周至少能保证3天的实习时间，心理学相关专业或对冥想/正念有研究同学优先； 2、对数字敏感，善于整理各类信息； 3、积极主动，结果导向，沟通力较强</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>市场调研、数据分析、用户研究</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9412,9 +8555,6 @@
           <t>Airflow、DataX、Flink、Hadoop、Hive、MySQL、SQL、Spark、云计算、大数据</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9457,9 +8597,6 @@
           <t>C、C++、CI/CD、Git、GitLab、Jenkins、Python</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9492,15 +8629,11 @@
           <t>【工作内容】 1. 支持eBay大中华区跨境电商卖家培训、商务拓展和品类管理团队完成包括客户管理、品牌宣传、平台部署和流程自动化完善等工作 2. 业务数据需求的分析、设计、落地，为业务提供决策支持 3. 制作并维护各个业务生态报表，结合项目需求和业务逻辑，提炼有效信息 【任职要求】 1. 对跨境电商运营和逻辑推理感兴趣 2. 精通Excel（包括但不限于：Pivot Table，Vlookup函数，动态图表等） 3. 英语水平优秀；沟通表达能力强，有文案写作经验者优先 4. 能够清晰地组织和规划工作，进行多任务处理，细致严谨，注重细节 5. 大三、大四本科生或研究生在读，每周出勤4天及以上，至少实习6个月 【薪资福利】 1. 本科生270元/天，研究生280元/天 2. 早餐、饮料、水果、零食、下午茶等一系列福利 3. 高大上的办公环境，超nice的team氛围，干货满满</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9533,11 +8666,6 @@
           <t>岗位职责：1.协助测试工程师完成语音冒烟测试和全功能测试 2.协助项目完成外部缺陷提交、分配、验证测试 任职要求： 1.性别不限，实习地点：上海市长宁区中山国际广场A栋304-305室，实习期间需保证正常出勤时间 2.具备良好的英语能力 3.具有良好的沟通能力，能够与测试工程师和测试经理等相关方保持良好的沟通，能接受短期出差 4.具有高度的责任心和时间管理意识，具有一定的抗压能力 5.保持良好的持续学习意识，可以按时完成安排的相关工作</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9570,11 +8698,6 @@
           <t>【岗位职责】 有机会参与客户沟通与视频的全流程制作，从选题策划、脚本创作，到后期剪辑、调色包装，都有你的发挥空间。 了解新媒体平台（视频号/抖音/微博/西瓜视频/快手等）的视频传播特点以及规则，有针对性地提出视频优化创意。 配合项目资料搜集以及创意执行落地。 【任职资格】 影视、动画、美术、编导、广电新闻等相关专业，熟悉脚本、摄像、剪辑、配音、包装等工作内容，有独自产出短视频经验者优先。 掌握Pr、AE、Ps等后期软件，基础拍摄能力，具有良好的审美及镜头感。 想法比技能更重要，希望你思维活跃，有良好的沟通表达能力与执行力，有个人图片/视频素材库优先。 【你将获得】 公关媒体行业运转的真实视角 以结果论，视频数据好实行额外奖励 一个友好团结的团队，与leader/老板日常交流的平台</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9607,15 +8730,11 @@
           <t>岗位职责（具体工作内容） 1、与网约车产品力营销团队共同打造创意传播事件，配合项目进行创意策划、用户洞察、热点分析等。 2、在小红书、抖音等社媒平台进行传播种草，协助brief整理、文案策划、社媒发布、达人运营等。 3、洞察用户需求，结合数据分析，发现和探索新的品牌喜爱度和业务增长手段。 4、协助跨部门沟通，处理部门日常行政事务。 任职资格（学历、目标院校、语言、技能、性格等要求） 1、大学本科及以上学历，广告、传媒、设计、社会学等相关专业，有营销传播相关实习经验优先。 2、网感好、有审美、具备创意思维、乐于思考与创新，熟悉主流社交平台内容生态及热点。 3、具有较好的逻辑分析能力，具备定性定量研究经验加分。</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>数据分析</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9648,11 +8767,6 @@
           <t>岗位职责： 1、分析用户的学习数据并进行深入诊断，提供个性化反馈和建议，帮助其实现科学备考； 2、持续监测用户学习行为数据，分析并制定教学及服务的改进方案； 3、通过与用户深度沟通，为雅思线上课程、服务体系的迭代提供有价值的信息输入。 任职资格： 1、26届及以后毕业的本科/研究生在校生，可尽快入职者优先； 2、雅思总分7.0及以上； 3、具备优秀的沟通能力，思维条理清晰，善于与他人寻求共识，能够接纳不同观点与反馈； 4、能够快速吸收新知识、新信息，并迁移应用； 5、实习期至少三个月，全勤到岗现场工作。 加分项： 1. 敏捷的反应能力，能够灵活应对突发情况； 2. 不错的反思能力，能够根据反馈和自我评估调整工作方式； 3. 出色的协作能力，能够理解并满足协作方需求，推动项目进展。</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9685,11 +8799,6 @@
           <t>你好，我是知行桥的合伙人&amp;CHO Kyle 很高兴你感兴趣我们的机会，知行桥（（InsightArc）是16年创业的企业知识服务公司，通过游学、讲师等服务连接中国企业和全球企业。 在这里，你可以接触到美国、日本、英国、芬兰、瑞典、新加坡等国的优秀企业和资深高管，共同服务国内头部的科技公司和创始人客户。我们的讲师包括前苹果联合创始人、前星巴克全球总裁、特斯拉联合创始人、前奈飞联合创始人、华大基因CEO、诺奖得主等。 我们在寻找一位市场营销实习生，参与打造以内容驱动增长的营销闭环，帮助知行桥完成从触达到转化的完整链路。优秀的同学未来可转为全职成员并承担更多渠道与项目职责，成长速度将与你的学习能力、自驱力和目标感高度相关。 这份工作的其他优势包括：与国际科技与商业品牌的近距离接触、深入参与从选题策划到转化落地的全过程、不断提升内容表达与市场分析能力，以及与一群自驱力强、执行力高、认真做事的团队伙伴一起成长。 你将参与的核心工作： 1. 文章内容创作：撰写公众号、LinkedIn、官网等内容与选题，提炼嘉宾与项目卖点，直接产出好的内容为客户创造价值。 2. 视频内容创作：参与短视频脚本、剪辑与素材整理，做好字幕语言翻译，支持产出好的视频内容为客户创造价值。 3. 流量与线索管理：参与流量来源梳理、线索整理与基础分析，对营销线索质量负责，协助提升有效线索数量与成交转化率。 4. 海外社媒管理</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9722,11 +8831,6 @@
           <t>岗位职责 1.参与固态导航雷达设备的技术协调、优化改进和试验等工作. 2.参与新体制导航雷达的开发工作. 任职资格 1. 熟悉固态雷达系统设计或信号处理，有相关工程经验者优先； 2. 有FPGA开发经验者优先； 3. 应届硕士或有相关工作经历的本科。</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9769,9 +8873,6 @@
           <t>PyTorch、TensorFlow、深度学习、计算机视觉</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9814,9 +8915,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9849,11 +8947,6 @@
           <t>1、我们是公司直招，不会以任何形式收任何费用； 2、工作内容：根据公司给的内容进行发布到各个平台即可，发布的内容都是经过专业人员审核，符合平台规范的； 3、工资多劳多得，按照发布平台计算； 4、是否可以开实习证明：满足实习条件，可以开具实习证明，表现优异者可以开具优秀实习生（在校生才能开实习证明，已经毕业的不行）； 5、可接受线上实习~</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9896,9 +8989,6 @@
           <t>C、C++、NumPy、Pandas、Python、Rust、TensorFlow、数据科学、机器学习、深度学习</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9941,9 +9031,6 @@
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9986,9 +9073,6 @@
           <t>SQL、数据分析</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10031,9 +9115,6 @@
           <t>Android、C、Embedding、Git、Java、Kotlin、PyTorch、Swift、TensorFlow、iOS、多模态、深度学习</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10076,9 +9157,6 @@
           <t>CSS、JavaScript、React、Vue、前端、数据分析</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10111,15 +9189,11 @@
           <t>职位描述 日常实习：面向全体在校生，为符合岗位要求的同学提供为期3个月及以上的项目实践机会。 团队介绍：抖音是一个帮助用户表达自我，记录美好生活的短视频平台。截至2021年6月，抖音日活跃用户超过6亿，并继续保持高速增长。加入我们，你将为亿万用户创造更好的产品，让用户看见更多样的世界。 1、负责抖音评论业务的策略相关工作，参与正向评论识别能力建设、完善正向评论数据基建，为提升抖音评论量、评论质量等核心指标负责； 2、通过评论画风理解与数据分析，总结各类型正向评论案例，归纳提炼共性特征辅助模型识别；分析用户兴趣与评论内容的相关性，为策略优化提供支持； 3、协同算法团队优化模型识别能力，将抽象的评论问题转化为明确的模型优化需求，参与方案讨论、需求拆解，协助验证模型效果，推动模型在评论场景的落地应用。 职位要求 1、本科及以上学历； 2、熟悉评论区互动逻辑，对评论内容有敏锐的洞察力，有内容创作或评论区运营相关经验更佳； 3、具备扎实的逻辑思维与抽象归纳能力，能从复杂的评论现象中提炼核心问题，清晰梳理问题脉络与归因； 4、熟练掌握SQL，有一定的数据分析能力； 5、自驱力强、责任心足，具备良好的学习能力与结果导向思维，善于主动发现问题并推动解决。</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>SQL、数据分析</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10162,9 +9236,6 @@
           <t>人工智能、内容运营、办公软件</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10207,9 +9278,6 @@
           <t>R、大数据、数据分析</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10242,15 +9310,11 @@
           <t>【职位描述】 参与有道业务的UI设计工作，为新功能、新产品提供创意及设计方案； 参与产品讨论，与产品经理、工程师协作，从视觉设计和用户体验的角度提出建议与解决方案； 全面跟进产研流程，与产品、研发、测试团队紧密协作，跟进设计方案落地，保证设计方案高度还原。 续关注设计趋势，主动挖掘视觉/体验问题，提出改进建议，提升产品设计品质。 【职位要求】 本科在读及以上学历，美术及设计相关专业; 熟悉Figma、Sketch、 Photoshop、 Al 等视觉设计软件；熟悉Web、iOS、 Android设计规范; 具备良好的视觉表现力和敏锐的趋势洞察力，能够提供较高质量的设计输出； 掌握设计相关的学科知识，能将知识应用于实际项目中，并能清晰地表达设计方案； 有系统化设计的意识和思考，能够考虑设计结果的完整性，能够通过复盘提炼通用性的经验方法； 简历请附上作品集。 【实习生工作内容】 参与主要负责部门设计需求及迭代相关界面设计，协助设计规范制定与审核； 参与项目沟通、方案设计，跟进落地上线；对接产品、开发等环节 主动挖掘视觉/体验问题，提出改进建议，提升产品设计品质</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>Android、iOS、产品设计、原型设计</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10283,15 +9347,11 @@
           <t>【团队介绍】 毕马威财务管理咨询服务为企业提供了战略财务、业务财务和运营财务“端到端”的解决方案，致力于通过研究行业最新发展趋势、应用新兴技术手段，协助企业提高其财务管理的精细化和智能化水平，从而支持企业财务运营效率和业务决策能力的提升，通过财务管理赋能产品研发、客户运营和营销展业。 【任职要求】 1. 国内外本科及以上学历在校生，拥有优异的学业表现，财务管理、会计、金融等相关专业； 2. 实习生尽快入职者优先，实习期3个月及以上优先，能够保证每周4天及以上的实习时间（全职实习优先）； 3. 银行业或会计核算管理相关实习工作经验，有管理咨询工作经验优先； 3. 有良好的英文听说读写能力，沟通技巧及团队合作精神； 4. 认真，细致，有责任心，逻辑思维缜密，对变化的商业环境有热情，学习能力强； 5. 熟练使用Excel和其他Microsoft Office软件，具有良好的PowerPoint技能优先考虑； 6. 能够接受项目出差需求； 【岗位职责】 1. 参与咨询方案规划工作； 2. 协助项目组完成项目交付工作，包括资料整理、行业研究、财务指标分析、数据分析、报告撰写等工作； 3. 协助准备项目汇报和相关的演示材料； 4. 参与内部会议，记录会议纪要； 5. 完成团队分配的其他相关工作；</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>Excel、PPT、人工智能、办公软件、市场调研、数据分析</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10324,11 +9384,6 @@
           <t>岗位职责 1. 老师一对一指导，完成内容制作和发布，反馈数据和截图 2. 根据指导，做相应配合 任职要求 1. 年龄满18周岁的在校大学生，专业不限 2. 常刷小红书/抖音，有基础网感 3. 态度认真，愿意跟着指导执行 薪资福利 • 50%收益分成：无底薪，账号税后收入直接对半分，按周结算 • 实习证明：期满3个月即可领取正规盖章版 • 表现优秀，可获得线下实习的推荐机会</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10361,15 +9416,11 @@
           <t>【团队工作介绍】 金融行业战略及数字化转型及实施咨询团队服务银行、保险、证券、投资集团（公司）及其他各类金融机构。我们通过提供从规划到实施落地的端到端服务，帮助客户拥抱数字化和创新，做好“五篇文章”，实现更好的业绩表现，提升经营效率，打造发展韧性和构建核心竞争力，从容应对快速变化的宏观经济及政策环境及内部变革的挑战。 【岗位职责】 1. 参与银行业务分析及相关交付设计； 2. 资料搜集整理、桌面研究、数据整理、产业分析等； 3. 访谈纪要整理； 4. 协助编写战略规划报告； 5. 其他项目所需的必要工作。 【工作地点】 杭州 【实习时间】 2026年2月 – 2026年7月（一周至少出勤4天，全勤优先） 【基本要求】 1. 国内外本科及以上学历在校生，专业不限，经济类、金融类、管理类专业优先； 2. 有优秀的展示和总结能力，能够清晰地向团队和管理层传达项目核心内容； 3. 能够非常熟练使用Microsoft Office套件； 4. 具备良好的沟通和人际交往能力，能够与不同背景的人有效合作； 5. 有咨询公司相关实习或项目经验者优先； 6. 具备很强的行业研究和分析洞察能力；</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>办公软件、市场调研</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10402,11 +9453,6 @@
           <t>【岗位职责】 1.参与无人机设计、试验试飞、装配与测试工作等； 2.完成部门负责人交付的其他工作。 【任职要求】 1.本科及以上学历在读学生，理工科背景，具体专业不限； 2.有航模相关经验优先； 3.良好的沟通能力、团队合作能力； 4.211/985优先考虑。 5.最好能实习半年及以上，一周到岗5天 【你将获得】 1.平台大，参与无人机设计研发的全过程，获得丰富的实习经验； 2.丰厚的实习补贴，200—350／天 3.工作环境好，氛围轻松，同事学历背景较好、工作能力强，可以学到很多东西。</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10439,11 +9485,6 @@
           <t>工作职责： 1、负责海外社交平台kol资源的开发，筛选合适的达人进行合作，负责kol合作选题、内容要点的策划等相关合作事宜； 2、维护与kol的长期良好合作关系，跟踪kol的推广活动效果，进行数据整理和分析。 职位要求 1、德语专业或者留学经历，德语可作为工作语言； 2、有kol达人对接经验，具备开发kol资源的能力； 3、具备丰富的短视频平台工作经验，有从0-1打造账号经历者优先考虑； 4、具备良好的网感，善于收集捕捉热点信息； 5、工作态度认真，责任感强，具有良好的团队意识、沟通能力和抗压能力。</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10476,11 +9517,6 @@
           <t>薪资待遇： 4000元/月 工作时间： 每周到岗3-5天 我们是谁： 一个专注于考试赛道的小红书创业团队。我们不搞虚头巴脑的心灵鸡汤，只讲干货、分享有用的商品。现在需要一个有过考公经验或者正在备考的实习生，用你的亲身经历来赋能内容。 你的日常工作： 1、精准找选题： 挖掘考试过程中大家真正焦虑的点（比如行测提速、申论模板、选岗困惑），结合平台热点出选题。 2、资料编辑与二创： 搜集并整理行业资料，将其优化成更接地气、更能引发备考党共鸣的小红书文案。（你需要知道哪些是真正的“刚需”，哪些是废话）。 我们希望你： 1、有过考公经历（无论是备战中、还是已上岸），熟悉行测、申论、公基等基本考试模块。 2、是小红书重度用户，懂什么叫网感，知道考生在小红书想看什么，有账号运营经验更佳。 3、执行力强，有一定的文字功底。 期待你的加入～</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10513,11 +9549,6 @@
           <t>岗位待遇： 1.工资待遇：底薪+阶梯式提成+绩效+补助+年终奖+冠军奖+课时费等，综合薪资6K-12K，上不封顶。 月入一万很正常，月入两万很容易，月入四万不是梦！ 2.员工福利：提供住宿+定期免费培训+高业绩员工三亚旅游+团队聚餐+内部球赛、另有意想不到的各种节日、生日福利。 3.晋升空间：主教练及课程研发方向。 岗位描述： 1.根据公司统一的教学方案对学员进行基础篮球个人技术、技战术演练、专业体能训练等。 2.增加学员兴趣，与学员和家长建立有效沟通，提升客户满意度。 3. 课余时间通过家长转介绍，线上线下渠道招收5—18岁的对篮球感兴趣学员。 4.负责球馆运营，维护球馆秩序。 岗位要求： 1. 有较强的教学实践能力，有较强的语言沟通能力，富有亲和力； 2. 为人诚恳，工作态度积极，踏实肯干； 3. 大专及以上学历，体育院校毕业，专业队教练，退役队员或具备其他相关技能和条件者优先录用。</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10550,11 +9581,6 @@
           <t>主要职责： 1、在媒体平台查找适合当下选题的文章，与版权方沟通授权事宜； 2、内容排版与视觉优化：负责公众号文章的日常排版与美化，熟练使用秀米、135编辑器或AI编辑器等工具，确保内容呈现的视觉品质与用户阅读体验。 3、内容发布与运营：独立完成公众号内容的定时推送、发布及日常维护，监测文章发布后的数据表现（如阅读量、点赞等）。 4、素材处理与工具应用，可使用PS等工具进行基本的图片处理与图文表格编辑。 5、内容辅助与协作：参与公众号的内容选题、素材搜集及相关投融资稿件撰写与发布等。与团队协作，完成其他微信端相关的支持工作。 任职要求： 1、会翻墙看外网热点或资料； 2、大三、大四或研究生在校生，新闻、传播、中文、市场营销等相关专业优先； 3、有微信公众号排版经验者优先，拥有一定的文案功底； 4、熟练使用公众号排版工具（如秀米、美图秀秀等）； 5、做事细致、负责，乐于学习； 6、能够保证稳定的实习时间，每周3-5天，长期合作，可线上。</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10587,15 +9613,11 @@
           <t>主要职责 1，项目计划和任务分配：协助项目经理制定项目计划，并帮助分配任务给团队成员，确保项目目标、范围和时间表的明确。 2. 采购管理和供应商管控。 订单处理：根据需求下达采购订单，确保订单信息准确无误。 供应商沟通：与供应商确认订单细节，包括交货日期、数量和价格等。 进度跟踪：跟踪订单的执行情况，确保按时交货，并处理任何可能出现的问题。 文件管理：维护和管理采购相关的文件和记录，如合同、订单、发票等。 异常处理：处理供应商交货异常和质量问题，确保物料符合要求。 对账与付款：协助财务部门对账，确保供应商发票和付款的准确性。 3文件管理：组织和维护项目文件，确保文件的准确性和完整性，并进行存档和备份. 任职要求 1.6个月实习期以上优先; 一周至少4天到岗实习 2. 有参与组织、沟通协调大中型活动者优先； 3. 项目管理、工业工程、电气工程等本科以上学生； 4.熟悉Microsoft系列常用办公软件者优先； 5.工作态度认真仔细，严谨，积极主动；</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
           <t>办公软件、项目管理</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10628,11 +9650,6 @@
           <t>1、根据IT基础设施建设所需的服务器、网络、IDC数据中心及其他IT产品需求，拆分梳理，基于供应情况，制定满足方案； 2、及时监控物料供应货期与状态，识别需求满足风险，发现预警，并推动落实供应保障举措，保证供需平衡； 3、梳理资源管理业务流程，输出需求文档，推动资源管理平台相关功能标准化、数字化。 4、协助完成与内部团队的日常对接与协调工作。</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10665,15 +9682,11 @@
           <t>【岗位职责】 负责公司 Social Agent 的全栈开发迭代 【岗位要求】 C 端基因：参与过完整的自研 C 端产品，对 H5/小程序的性能优化有实战经验。 跨端能力：熟悉 Taro 等跨端方案，能处理好不同平台（微信/抖音/H5）的差异性。 硬核栈：Golang / Java 为主。我们不看重你会多少种语言，看重你处理一致性、幂等性和分布式事务的内功。 中间件：对 MySQL 优化、Redis 缓存策略、Kafka 消息堆积处理有实操经验，而不是仅仅听过名词。 自驱：能目标驱动地完成事情，并灵活地与同事协作、无需人盯 自信：无条件地相信自己一定能在岗位专业上做到业内顶尖水平 【加分项】 开源社区活跃分子：在 GitHub 上有持续维护的项目，或者给知名项目贡献过 PR（请附上 ID）。 技术布道者：拥有长期更新的技术博客或专栏 新技术的发烧友：对 Agent 有浓厚兴趣，AI Coding 重度用户 自驱动创造者：有过独立开发产品（甚至只是个小工具）并上线运营的经历</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>Git、Go、Java、Kafka、MySQL、Redis、人工智能、全栈、小程序</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10716,9 +9729,6 @@
           <t>人工智能</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
